--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -346,7 +346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K213"/>
+  <dimension ref="A1:K223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -7504,18 +7504,18 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>480553055894.4</v>
+        <v>17377625281.2</v>
       </c>
       <c r="F147" t="n">
-        <v>46.6</v>
+        <v>62.2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>17377625281.2</v>
+        <v>21174462628.9</v>
       </c>
       <c r="F148" t="n">
-        <v>62.2</v>
+        <v>21.8</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7602,32 +7602,32 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>643008821970.1</v>
+        <v>23995112795.7</v>
       </c>
       <c r="F149" t="n">
-        <v>33.8</v>
+        <v>13.3</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -7651,32 +7651,32 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>21174462628.9</v>
+        <v>30594008765.7</v>
       </c>
       <c r="F150" t="n">
-        <v>21.8</v>
+        <v>27.5</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7700,32 +7700,32 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>746784015747.9</v>
+        <v>42404519909.6</v>
       </c>
       <c r="F151" t="n">
-        <v>16.1</v>
+        <v>38.6</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>23995112795.7</v>
+        <v>53033212824.9</v>
       </c>
       <c r="F152" t="n">
-        <v>13.3</v>
+        <v>25.1</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -7798,32 +7798,32 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>930306187617.9</v>
+        <v>63408630581.9</v>
       </c>
       <c r="F153" t="n">
-        <v>24.6</v>
+        <v>19.6</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7847,32 +7847,32 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>30594008765.7</v>
+        <v>79061685127.39999</v>
       </c>
       <c r="F154" t="n">
-        <v>27.5</v>
+        <v>24.7</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7896,32 +7896,32 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1195582997017.2</v>
+        <v>101126220212.8</v>
       </c>
       <c r="F155" t="n">
-        <v>28.5</v>
+        <v>27.9</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7945,32 +7945,32 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>42404519909.6</v>
+        <v>131945447084.8</v>
       </c>
       <c r="F156" t="n">
-        <v>38.6</v>
+        <v>30.5</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7994,32 +7994,32 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C157" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1383038455119.5</v>
+        <v>184682722830.1</v>
       </c>
       <c r="F157" t="n">
-        <v>15.7</v>
+        <v>40</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -8043,32 +8043,32 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>53033212824.9</v>
+        <v>327767509170</v>
       </c>
       <c r="F158" t="n">
-        <v>25.1</v>
+        <v>77.5</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>2021</v>
       </c>
       <c r="C159" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1613383509819.7</v>
+        <v>480553055894.4</v>
       </c>
       <c r="F159" t="n">
-        <v>16.7</v>
+        <v>46.6</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -8141,32 +8141,32 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>2021</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>63408630581.9</v>
+        <v>643008821970.1</v>
       </c>
       <c r="F160" t="n">
-        <v>19.6</v>
+        <v>33.8</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -8190,32 +8190,32 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>2021</v>
       </c>
       <c r="C161" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1932171957524.9</v>
+        <v>746784015747.9</v>
       </c>
       <c r="F161" t="n">
-        <v>19.8</v>
+        <v>16.1</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -8239,32 +8239,32 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>2021</v>
       </c>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>79061685127.39999</v>
+        <v>930306187617.9</v>
       </c>
       <c r="F162" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -8288,32 +8288,32 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>2021</v>
       </c>
       <c r="C163" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2069027697276.4</v>
+        <v>1195582997017.2</v>
       </c>
       <c r="F163" t="n">
-        <v>7.1</v>
+        <v>28.5</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8337,32 +8337,32 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>2021</v>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>101126220212.8</v>
+        <v>1383038455119.5</v>
       </c>
       <c r="F164" t="n">
-        <v>27.9</v>
+        <v>15.7</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8386,32 +8386,32 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>2021</v>
       </c>
       <c r="C165" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2210425050108.3</v>
+        <v>1613383509819.7</v>
       </c>
       <c r="F165" t="n">
-        <v>6.8</v>
+        <v>16.7</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8435,32 +8435,32 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>2021</v>
       </c>
       <c r="C166" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>131945447084.8</v>
+        <v>1932171957524.9</v>
       </c>
       <c r="F166" t="n">
-        <v>30.5</v>
+        <v>19.8</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -8484,32 +8484,32 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>2021</v>
       </c>
       <c r="C167" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2396255484070.9</v>
+        <v>2069027697276.4</v>
       </c>
       <c r="F167" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -8533,32 +8533,32 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>2021</v>
       </c>
       <c r="C168" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>184682722830.1</v>
+        <v>2210425050108.3</v>
       </c>
       <c r="F168" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -8582,32 +8582,32 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>2021</v>
       </c>
       <c r="C169" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2577508248886</v>
+        <v>2396255484070.9</v>
       </c>
       <c r="F169" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>327767509170</v>
+        <v>2577508248886</v>
       </c>
       <c r="F170" t="n">
-        <v>77.5</v>
+        <v>7.6</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -9856,18 +9856,18 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>281565112063483</v>
+        <v>25379624724721.4</v>
       </c>
       <c r="F195" t="n">
-        <v>32.6</v>
+        <v>1.7</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -9905,32 +9905,32 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>40521840708458.3</v>
+        <v>25684975429035.5</v>
       </c>
       <c r="F196" t="n">
-        <v>9.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -9954,32 +9954,32 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>25379624724721.4</v>
+        <v>25986417377849.1</v>
       </c>
       <c r="F197" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -10003,33 +10003,33 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C198" t="n">
+        <v>4</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>26516834159241.7</v>
+      </c>
+      <c r="F198" t="n">
         <v>2</v>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Febrero</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
-        <v>322703709401564</v>
-      </c>
-      <c r="F198" t="n">
-        <v>14.6</v>
-      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>Índice base diciembre 2007=100 y variación mensual %</t>
@@ -10052,32 +10052,32 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C199" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>44948592993158.4</v>
+        <v>26903972496868.1</v>
       </c>
       <c r="F199" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -10101,32 +10101,32 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Febrero</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>25684975429035.5</v>
+        <v>27162536873498.1</v>
       </c>
       <c r="F200" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -10150,32 +10150,32 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C201" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Julio</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>364960489482614</v>
+        <v>27366064708317.6</v>
       </c>
       <c r="F201" t="n">
-        <v>13.1</v>
+        <v>0.7</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -10199,32 +10199,32 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Agosto</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>48695941027700.9</v>
+        <v>27746667522384.2</v>
       </c>
       <c r="F202" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -10248,32 +10248,32 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C203" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Marzo</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>25986417377849.1</v>
+        <v>27972976631499.6</v>
       </c>
       <c r="F203" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -10297,33 +10297,33 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C204" t="n">
+        <v>10</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>29100339690082.1</v>
+      </c>
+      <c r="F204" t="n">
         <v>4</v>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Abril</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
-        <v>403528566746262</v>
-      </c>
-      <c r="F204" t="n">
-        <v>10.6</v>
-      </c>
       <c r="G204" t="inlineStr">
         <is>
           <t>Índice base diciembre 2007=100 y variación mensual %</t>
@@ -10346,32 +10346,32 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C205" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>56686369544411.3</v>
+        <v>33516689669759.1</v>
       </c>
       <c r="F205" t="n">
-        <v>16.4</v>
+        <v>15.2</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -10395,32 +10395,32 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C206" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Abril</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>26516834159241.7</v>
+        <v>36919909673224.9</v>
       </c>
       <c r="F206" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -10444,32 +10444,32 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>428967191622142.1</v>
+        <v>40521840708458.3</v>
       </c>
       <c r="F207" t="n">
-        <v>6.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -10493,32 +10493,32 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C208" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>68691300824090.4</v>
+        <v>44948592993158.4</v>
       </c>
       <c r="F208" t="n">
-        <v>21.2</v>
+        <v>10.9</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -10542,32 +10542,32 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C209" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Mayo</t>
+          <t>Marzo</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>26903972496868.1</v>
+        <v>48695941027700.9</v>
       </c>
       <c r="F209" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -10591,32 +10591,32 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C210" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Abril</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>75780386243945.11</v>
+        <v>56686369544411.3</v>
       </c>
       <c r="F210" t="n">
-        <v>10.3</v>
+        <v>16.4</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -10640,32 +10640,32 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C211" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Junio</t>
+          <t>Mayo</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>27162536873498.1</v>
+        <v>68691300824090.4</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>21.2</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -10689,32 +10689,32 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C212" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Julio</t>
+          <t>Junio</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>86578516564082.41</v>
+        <v>75780386243945.11</v>
       </c>
       <c r="F212" t="n">
-        <v>14.2</v>
+        <v>10.3</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -10738,18 +10738,18 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C213" t="n">
         <v>7</v>
@@ -10760,10 +10760,10 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>27366064708317.6</v>
+        <v>86578516564082.41</v>
       </c>
       <c r="F213" t="n">
-        <v>0.7</v>
+        <v>14.2</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -10787,7 +10787,497 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C214" t="n">
+        <v>8</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>100503985890336</v>
+      </c>
+      <c r="F214" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C215" t="n">
+        <v>9</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>122169616603139</v>
+      </c>
+      <c r="F215" t="n">
+        <v>21.55698654224845</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C216" t="n">
+        <v>10</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>153849788402697</v>
+      </c>
+      <c r="F216" t="n">
+        <v>25.93130164472011</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C217" t="n">
+        <v>11</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>187021825372618</v>
+      </c>
+      <c r="F217" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C218" t="n">
+        <v>12</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>212393273459827</v>
+      </c>
+      <c r="F218" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>281565112063483</v>
+      </c>
+      <c r="F219" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C220" t="n">
+        <v>2</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>322703709401564</v>
+      </c>
+      <c r="F220" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>364960489482614</v>
+      </c>
+      <c r="F221" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>403528566746262</v>
+      </c>
+      <c r="F222" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C223" t="n">
+        <v>5</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>428967191622142.1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -10885,7 +11375,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08T07:58:53Z</t>
+          <t>2026-07-08T10:50:35Z</t>
         </is>
       </c>
     </row>
@@ -10909,7 +11399,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -10920,7 +11410,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -10931,7 +11421,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 27366064708317.6, "monthly_variation_pct": 0.7, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-08T07:58:53Z"}</t>
+          <t>{"date": "2026-05-01", "year": 2026, "month": 5, "month_name": "Mayo", "index_value": 428967191622142.06, "monthly_variation_pct": 6.3, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-08T10:50:35Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08T10:50:35Z</t>
+          <t>2026-07-15T08:47:24Z</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"date": "2026-05-01", "year": 2026, "month": 5, "month_name": "Mayo", "index_value": 428967191622142.06, "monthly_variation_pct": 6.3, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-08T10:50:35Z"}</t>
+          <t>{"date": "2026-05-01", "year": 2026, "month": 5, "month_name": "Mayo", "index_value": 428967191622142.06, "monthly_variation_pct": 6.3, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-15T08:47:24Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +86,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -536,10 +551,10 @@
           <t>2007-12-01</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="7" t="n">
         <v>2007</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -547,7 +562,7 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="4" t="n"/>
@@ -583,10 +598,10 @@
           <t>2008-01-01</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -594,10 +609,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="8" t="n">
         <v>103.1</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="8" t="n">
         <v>3.1</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -632,10 +647,10 @@
           <t>2008-02-01</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -643,10 +658,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="8" t="n">
         <v>105.3</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -681,10 +696,10 @@
           <t>2008-03-01</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -692,10 +707,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="8" t="n">
         <v>107.1</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -730,10 +745,10 @@
           <t>2008-04-01</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -741,10 +756,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="8" t="n">
         <v>108.9</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -779,10 +794,10 @@
           <t>2008-05-01</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -790,10 +805,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="8" t="n">
         <v>112.4</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="8" t="n">
         <v>3.2</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -828,10 +843,10 @@
           <t>2008-06-01</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -839,10 +854,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="8" t="n">
         <v>115.1</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -877,10 +892,10 @@
           <t>2008-07-01</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -888,10 +903,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="8" t="n">
         <v>117.3</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -926,10 +941,10 @@
           <t>2008-08-01</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -937,10 +952,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="8" t="n">
         <v>119.4</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -975,10 +990,10 @@
           <t>2008-09-01</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -986,10 +1001,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="8" t="n">
         <v>121.8</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1024,10 +1039,10 @@
           <t>2008-10-01</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1035,10 +1050,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="8" t="n">
         <v>124.7</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1073,10 +1088,10 @@
           <t>2008-11-01</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1084,10 +1099,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="8" t="n">
         <v>127.6</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="8" t="n">
         <v>2.3</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1122,10 +1137,10 @@
           <t>2008-12-01</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="7" t="n">
         <v>2008</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1133,10 +1148,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="8" t="n">
         <v>130.9</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1171,10 +1186,10 @@
           <t>2009-01-01</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1182,10 +1197,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="8" t="n">
         <v>133.9</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="8" t="n">
         <v>2.3</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1220,10 +1235,10 @@
           <t>2009-02-01</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1231,10 +1246,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="8" t="n">
         <v>135.6</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="8" t="n">
         <v>1.3</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1269,10 +1284,10 @@
           <t>2009-03-01</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1280,10 +1295,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="8" t="n">
         <v>137.2</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1318,10 +1333,10 @@
           <t>2009-04-01</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1329,10 +1344,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="8" t="n">
         <v>139.7</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1367,10 +1382,10 @@
           <t>2009-05-01</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1378,10 +1393,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="8" t="n">
         <v>142.5</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1416,10 +1431,10 @@
           <t>2009-06-01</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1427,10 +1442,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="7" t="n">
         <v>145</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1465,10 +1480,10 @@
           <t>2009-07-01</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1476,10 +1491,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="7" t="n">
         <v>148</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="8" t="n">
         <v>2.1</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1514,10 +1529,10 @@
           <t>2009-08-01</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1525,10 +1540,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="8" t="n">
         <v>151.3</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1563,10 +1578,10 @@
           <t>2009-09-01</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1574,10 +1589,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="8" t="n">
         <v>155.1</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1612,10 +1627,10 @@
           <t>2009-10-01</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1623,10 +1638,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="7" t="n">
         <v>158</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1661,10 +1676,10 @@
           <t>2009-11-01</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1672,10 +1687,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="8" t="n">
         <v>1.9</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1710,10 +1725,10 @@
           <t>2009-12-01</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="7" t="n">
         <v>2009</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1721,10 +1736,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="8" t="n">
         <v>163.7</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -1759,10 +1774,10 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1770,10 +1785,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="8" t="n">
         <v>166.5</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -1808,10 +1823,10 @@
           <t>2010-02-01</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1819,10 +1834,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="8" t="n">
         <v>169.1</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -1857,10 +1872,10 @@
           <t>2010-03-01</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1868,10 +1883,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="8" t="n">
         <v>173.2</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -1906,10 +1921,10 @@
           <t>2010-04-01</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n">
+      <c r="B35" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1917,10 +1932,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="8" t="n">
         <v>182.2</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="8" t="n">
         <v>5.2</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -1955,10 +1970,10 @@
           <t>2010-05-01</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1966,10 +1981,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="7" t="n">
         <v>187</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2004,10 +2019,10 @@
           <t>2010-06-01</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2015,10 +2030,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="8" t="n">
         <v>190.4</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2053,10 +2068,10 @@
           <t>2010-07-01</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n">
+      <c r="B38" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2064,10 +2079,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="8" t="n">
         <v>193.1</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2102,10 +2117,10 @@
           <t>2010-08-01</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n">
+      <c r="B39" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2113,10 +2128,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="8" t="n">
         <v>196.2</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2151,10 +2166,10 @@
           <t>2010-09-01</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2162,10 +2177,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="8" t="n">
         <v>198.4</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2200,10 +2215,10 @@
           <t>2010-10-01</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n">
+      <c r="B41" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2211,10 +2226,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="8" t="n">
         <v>201.4</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2249,10 +2264,10 @@
           <t>2010-11-01</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n">
+      <c r="B42" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2260,10 +2275,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="8" t="n">
         <v>204.5</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2298,10 +2313,10 @@
           <t>2010-12-01</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n">
+      <c r="B43" s="7" t="n">
         <v>2010</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2309,10 +2324,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="8" t="n">
         <v>208.2</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2347,10 +2362,10 @@
           <t>2011-01-01</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2358,10 +2373,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="8" t="n">
         <v>213.9</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2396,10 +2411,10 @@
           <t>2011-02-01</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2407,10 +2422,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="8" t="n">
         <v>217.6</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2445,10 +2460,10 @@
           <t>2011-03-01</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n">
+      <c r="B46" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2456,10 +2471,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="8" t="n">
         <v>220.7</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2494,10 +2509,10 @@
           <t>2011-04-01</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n">
+      <c r="B47" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2505,10 +2520,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="8" t="n">
         <v>223.9</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -2543,10 +2558,10 @@
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B48" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2554,10 +2569,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="8" t="n">
         <v>229.6</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -2592,10 +2607,10 @@
           <t>2011-06-01</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n">
+      <c r="B49" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2603,10 +2618,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="8" t="n">
         <v>235.3</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="8" t="n">
         <v>2.5</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -2641,10 +2656,10 @@
           <t>2011-07-01</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B50" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2652,10 +2667,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="8" t="n">
         <v>241.6</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="8" t="n">
         <v>2.7</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -2690,10 +2705,10 @@
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n">
+      <c r="B51" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2701,10 +2716,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="8" t="n">
         <v>246.9</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2739,10 +2754,10 @@
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B52" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C52" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2750,10 +2765,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="8" t="n">
         <v>250.9</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2788,10 +2803,10 @@
           <t>2011-10-01</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C53" s="4" t="n">
+      <c r="C53" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2799,10 +2814,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="8" t="n">
         <v>255.5</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2837,10 +2852,10 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2848,10 +2863,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="7" t="n">
         <v>261</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2886,10 +2901,10 @@
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n">
+      <c r="B55" s="7" t="n">
         <v>2011</v>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="C55" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2897,10 +2912,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="8" t="n">
         <v>265.6</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -2935,10 +2950,10 @@
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n">
+      <c r="B56" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2946,10 +2961,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="8" t="n">
         <v>269.6</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="F56" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -2984,10 +2999,10 @@
           <t>2012-02-01</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2995,10 +3010,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="8" t="n">
         <v>272.6</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3033,10 +3048,10 @@
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n">
+      <c r="B58" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3044,10 +3059,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="7" t="n">
         <v>275</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="8" t="n">
         <v>0.9</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3082,10 +3097,10 @@
           <t>2012-04-01</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n">
+      <c r="B59" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C59" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3093,10 +3108,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="8" t="n">
         <v>277.2</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3131,10 +3146,10 @@
           <t>2012-05-01</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3142,10 +3157,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="8" t="n">
         <v>281.5</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3180,10 +3195,10 @@
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="B61" s="4" t="n">
+      <c r="B61" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C61" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3191,10 +3206,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="8" t="n">
         <v>285.5</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3229,10 +3244,10 @@
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n">
+      <c r="B62" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C62" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3240,10 +3255,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="8" t="n">
         <v>288.4</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3278,10 +3293,10 @@
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n">
+      <c r="B63" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C63" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3289,10 +3304,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="8" t="n">
         <v>291.5</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="8" t="n">
         <v>1.1</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3327,10 +3342,10 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3338,10 +3353,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="8" t="n">
         <v>296.1</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -3376,10 +3391,10 @@
           <t>2012-10-01</t>
         </is>
       </c>
-      <c r="B65" s="4" t="n">
+      <c r="B65" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3387,10 +3402,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="8" t="n">
         <v>301.2</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3425,10 +3440,10 @@
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="B66" s="4" t="n">
+      <c r="B66" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3436,10 +3451,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="8" t="n">
         <v>308.1</v>
       </c>
-      <c r="F66" s="4" t="n">
+      <c r="F66" s="8" t="n">
         <v>2.3</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -3474,10 +3489,10 @@
           <t>2012-12-01</t>
         </is>
       </c>
-      <c r="B67" s="4" t="n">
+      <c r="B67" s="7" t="n">
         <v>2012</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C67" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3485,10 +3500,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="8" t="n">
         <v>318.9</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="F67" s="8" t="n">
         <v>3.5</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3523,10 +3538,10 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n">
+      <c r="B68" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3534,10 +3549,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="8" t="n">
         <v>329.4</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="8" t="n">
         <v>3.3</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -3572,10 +3587,10 @@
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="B69" s="4" t="n">
+      <c r="B69" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C69" s="4" t="n">
+      <c r="C69" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3583,10 +3598,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="8" t="n">
         <v>334.8</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3621,10 +3636,10 @@
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="B70" s="4" t="n">
+      <c r="B70" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C70" s="4" t="n">
+      <c r="C70" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3632,10 +3647,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="8" t="n">
         <v>344.1</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="8" t="n">
         <v>2.8</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -3670,10 +3685,10 @@
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n">
+      <c r="B71" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C71" s="4" t="n">
+      <c r="C71" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3681,10 +3696,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="8" t="n">
         <v>358.8</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="8" t="n">
         <v>4.3</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -3719,10 +3734,10 @@
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3730,10 +3745,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="8" t="n">
         <v>380.7</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="8" t="n">
         <v>6.1</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -3768,10 +3783,10 @@
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="C73" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3779,10 +3794,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="8" t="n">
         <v>398.6</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="8" t="n">
         <v>4.7</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3817,10 +3832,10 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="B74" s="4" t="n">
+      <c r="B74" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3828,10 +3843,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="8" t="n">
         <v>411.3</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="8" t="n">
         <v>3.2</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -3866,10 +3881,10 @@
           <t>2013-08-01</t>
         </is>
       </c>
-      <c r="B75" s="4" t="n">
+      <c r="B75" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C75" s="4" t="n">
+      <c r="C75" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3877,10 +3892,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="8" t="n">
         <v>423.7</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -3915,10 +3930,10 @@
           <t>2013-09-01</t>
         </is>
       </c>
-      <c r="B76" s="4" t="n">
+      <c r="B76" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C76" s="4" t="n">
+      <c r="C76" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3926,10 +3941,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="8" t="n">
         <v>442.3</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="8" t="n">
         <v>4.4</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -3964,10 +3979,10 @@
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C77" s="4" t="n">
+      <c r="C77" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3975,10 +3990,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="E77" s="8" t="n">
         <v>464.9</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="F77" s="8" t="n">
         <v>5.1</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4013,10 +4028,10 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="B78" s="4" t="n">
+      <c r="B78" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C78" s="4" t="n">
+      <c r="C78" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4024,10 +4039,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E78" s="4" t="n">
+      <c r="E78" s="8" t="n">
         <v>487.3</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4062,10 +4077,10 @@
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="B79" s="4" t="n">
+      <c r="B79" s="7" t="n">
         <v>2013</v>
       </c>
-      <c r="C79" s="4" t="n">
+      <c r="C79" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4073,10 +4088,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="8" t="n">
         <v>498.1</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4111,10 +4126,10 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="B80" s="4" t="n">
+      <c r="B80" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C80" s="4" t="n">
+      <c r="C80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4122,10 +4137,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="8" t="n">
         <v>514.7</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="8" t="n">
         <v>3.3</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4160,10 +4175,10 @@
           <t>2014-02-01</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n">
+      <c r="B81" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C81" s="4" t="n">
+      <c r="C81" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4171,10 +4186,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="8" t="n">
         <v>526.8</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4209,10 +4224,10 @@
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n">
+      <c r="B82" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C82" s="4" t="n">
+      <c r="C82" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4220,10 +4235,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="8" t="n">
         <v>548.3</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="8" t="n">
         <v>4.1</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -4258,10 +4273,10 @@
           <t>2014-04-01</t>
         </is>
       </c>
-      <c r="B83" s="4" t="n">
+      <c r="B83" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C83" s="4" t="n">
+      <c r="C83" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4269,10 +4284,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="8" t="n">
         <v>579.4</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="8" t="n">
         <v>5.7</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4307,10 +4322,10 @@
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4318,10 +4333,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="8" t="n">
         <v>612.6</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="8" t="n">
         <v>5.7</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -4356,10 +4371,10 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="B85" s="4" t="n">
+      <c r="B85" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C85" s="4" t="n">
+      <c r="C85" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4367,10 +4382,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="8" t="n">
         <v>639.7</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="8" t="n">
         <v>4.4</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4405,10 +4420,10 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B86" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C86" s="4" t="n">
+      <c r="C86" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4416,10 +4431,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="8" t="n">
         <v>666.2</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="8" t="n">
         <v>4.1</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -4454,10 +4469,10 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B87" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C87" s="4" t="n">
+      <c r="C87" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -4465,10 +4480,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="8" t="n">
         <v>692.4</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4503,10 +4518,10 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="B88" s="4" t="n">
+      <c r="B88" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C88" s="4" t="n">
+      <c r="C88" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4514,10 +4529,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="E88" s="8" t="n">
         <v>725.4</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -4552,10 +4567,10 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="B89" s="4" t="n">
+      <c r="B89" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C89" s="4" t="n">
+      <c r="C89" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4563,10 +4578,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E89" s="4" t="n">
+      <c r="E89" s="8" t="n">
         <v>761.8</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4601,10 +4616,10 @@
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="B90" s="4" t="n">
+      <c r="B90" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C90" s="4" t="n">
+      <c r="C90" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4612,10 +4627,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="8" t="n">
         <v>797.3</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="8" t="n">
         <v>4.7</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -4650,10 +4665,10 @@
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="B91" s="4" t="n">
+      <c r="B91" s="7" t="n">
         <v>2014</v>
       </c>
-      <c r="C91" s="4" t="n">
+      <c r="C91" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4661,10 +4676,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="8" t="n">
         <v>839.5</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="8" t="n">
         <v>5.3</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4699,10 +4714,10 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="B92" s="4" t="n">
+      <c r="B92" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C92" s="4" t="n">
+      <c r="C92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -4710,10 +4725,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E92" s="4" t="n">
+      <c r="E92" s="8" t="n">
         <v>904.8</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="F92" s="8" t="n">
         <v>7.8</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -4748,10 +4763,10 @@
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="B93" s="4" t="n">
+      <c r="B93" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C93" s="4" t="n">
+      <c r="C93" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4759,10 +4774,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="8" t="n">
         <v>949.1</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" s="8" t="n">
         <v>4.9</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4797,10 +4812,10 @@
           <t>2015-03-01</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n">
+      <c r="B94" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C94" s="4" t="n">
+      <c r="C94" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4808,10 +4823,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="8" t="n">
         <v>1000.2</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -4846,10 +4861,10 @@
           <t>2015-04-01</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n">
+      <c r="B95" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C95" s="4" t="n">
+      <c r="C95" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4857,10 +4872,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="8" t="n">
         <v>1063.8</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="8" t="n">
         <v>6.4</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4895,10 +4910,10 @@
           <t>2015-05-01</t>
         </is>
       </c>
-      <c r="B96" s="4" t="n">
+      <c r="B96" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C96" s="4" t="n">
+      <c r="C96" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4906,10 +4921,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="8" t="n">
         <v>1148.8</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="7" t="n">
         <v>8</v>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -4944,10 +4959,10 @@
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B97" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C97" s="4" t="n">
+      <c r="C97" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4955,10 +4970,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="8" t="n">
         <v>1261.6</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4993,10 +5008,10 @@
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="B98" s="4" t="n">
+      <c r="B98" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C98" s="4" t="n">
+      <c r="C98" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -5004,10 +5019,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="8" t="n">
         <v>1397.5</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -5042,10 +5057,10 @@
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="B99" s="4" t="n">
+      <c r="B99" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C99" s="4" t="n">
+      <c r="C99" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5053,10 +5068,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E99" s="4" t="n">
+      <c r="E99" s="8" t="n">
         <v>1570.8</v>
       </c>
-      <c r="F99" s="4" t="n">
+      <c r="F99" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -5091,10 +5106,10 @@
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n">
+      <c r="B100" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C100" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5102,10 +5117,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E100" s="4" t="n">
+      <c r="E100" s="8" t="n">
         <v>1752.1</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -5140,10 +5155,10 @@
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="B101" s="4" t="n">
+      <c r="B101" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C101" s="4" t="n">
+      <c r="C101" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5151,10 +5166,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="8" t="n">
         <v>1951.3</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -5189,10 +5204,10 @@
           <t>2015-11-01</t>
         </is>
       </c>
-      <c r="B102" s="4" t="n">
+      <c r="B102" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C102" s="4" t="n">
+      <c r="C102" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5200,10 +5215,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="8" t="n">
         <v>2168.5</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -5238,10 +5253,10 @@
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="B103" s="4" t="n">
+      <c r="B103" s="7" t="n">
         <v>2015</v>
       </c>
-      <c r="C103" s="4" t="n">
+      <c r="C103" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5249,10 +5264,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="8" t="n">
         <v>2357.9</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="F103" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -5287,10 +5302,10 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="B104" s="4" t="n">
+      <c r="B104" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C104" s="4" t="n">
+      <c r="C104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5298,10 +5313,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E104" s="4" t="n">
+      <c r="E104" s="8" t="n">
         <v>2576.5</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -5336,10 +5351,10 @@
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="B105" s="4" t="n">
+      <c r="B105" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C105" s="4" t="n">
+      <c r="C105" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -5347,10 +5362,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="8" t="n">
         <v>2801.1</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5385,10 +5400,10 @@
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n">
+      <c r="B106" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C106" s="4" t="n">
+      <c r="C106" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -5396,10 +5411,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E106" s="4" t="n">
+      <c r="E106" s="8" t="n">
         <v>3096.2</v>
       </c>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -5434,10 +5449,10 @@
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n">
+      <c r="B107" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C107" s="4" t="n">
+      <c r="C107" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -5445,10 +5460,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="8" t="n">
         <v>3541.6</v>
       </c>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5483,10 +5498,10 @@
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="B108" s="4" t="n">
+      <c r="B108" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C108" s="4" t="n">
+      <c r="C108" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -5494,10 +5509,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E108" s="4" t="n">
+      <c r="E108" s="8" t="n">
         <v>4195.9</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="F108" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -5532,10 +5547,10 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="B109" s="4" t="n">
+      <c r="B109" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C109" s="4" t="n">
+      <c r="C109" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -5543,10 +5558,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="8" t="n">
         <v>5001.5</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -5581,10 +5596,10 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="B110" s="4" t="n">
+      <c r="B110" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C110" s="4" t="n">
+      <c r="C110" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -5592,10 +5607,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E110" s="4" t="n">
+      <c r="E110" s="8" t="n">
         <v>5437.1</v>
       </c>
-      <c r="F110" s="4" t="n">
+      <c r="F110" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -5630,10 +5645,10 @@
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="B111" s="4" t="n">
+      <c r="B111" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C111" s="4" t="n">
+      <c r="C111" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -5641,10 +5656,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E111" s="4" t="n">
+      <c r="E111" s="8" t="n">
         <v>5825.7</v>
       </c>
-      <c r="F111" s="4" t="n">
+      <c r="F111" s="8" t="n">
         <v>7.1</v>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -5679,10 +5694,10 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C112" s="4" t="n">
+      <c r="C112" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -5690,10 +5705,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E112" s="4" t="n">
+      <c r="E112" s="8" t="n">
         <v>6364.4</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -5728,10 +5743,10 @@
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="B113" s="4" t="n">
+      <c r="B113" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C113" s="4" t="n">
+      <c r="C113" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -5739,10 +5754,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="8" t="n">
         <v>6873.9</v>
       </c>
-      <c r="F113" s="4" t="n">
+      <c r="F113" s="7" t="n">
         <v>8</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5777,10 +5792,10 @@
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n">
+      <c r="B114" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C114" s="4" t="n">
+      <c r="C114" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -5788,10 +5803,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E114" s="4" t="n">
+      <c r="E114" s="8" t="n">
         <v>7668.9</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -5826,10 +5841,10 @@
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n">
+      <c r="B115" s="7" t="n">
         <v>2016</v>
       </c>
-      <c r="C115" s="4" t="n">
+      <c r="C115" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -5837,10 +5852,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="8" t="n">
         <v>8826.9</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5875,10 +5890,10 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="B116" s="4" t="n">
+      <c r="B116" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C116" s="4" t="n">
+      <c r="C116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -5886,10 +5901,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E116" s="4" t="n">
+      <c r="E116" s="8" t="n">
         <v>10378.1</v>
       </c>
-      <c r="F116" s="4" t="n">
+      <c r="F116" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -5924,10 +5939,10 @@
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n">
+      <c r="B117" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C117" s="4" t="n">
+      <c r="C117" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -5935,10 +5950,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="8" t="n">
         <v>11697.2</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -5973,10 +5988,10 @@
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="B118" s="4" t="n">
+      <c r="B118" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C118" s="4" t="n">
+      <c r="C118" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -5984,10 +5999,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E118" s="4" t="n">
+      <c r="E118" s="8" t="n">
         <v>12910.1</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6022,10 +6037,10 @@
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="B119" s="4" t="n">
+      <c r="B119" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C119" s="4" t="n">
+      <c r="C119" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -6033,10 +6048,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="8" t="n">
         <v>13975.9</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -6071,10 +6086,10 @@
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="B120" s="4" t="n">
+      <c r="B120" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C120" s="4" t="n">
+      <c r="C120" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -6082,10 +6097,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E120" s="4" t="n">
+      <c r="E120" s="8" t="n">
         <v>15610.4</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -6120,10 +6135,10 @@
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="B121" s="4" t="n">
+      <c r="B121" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C121" s="4" t="n">
+      <c r="C121" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -6131,10 +6146,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E121" s="4" t="n">
+      <c r="E121" s="8" t="n">
         <v>17537.8</v>
       </c>
-      <c r="F121" s="4" t="n">
+      <c r="F121" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -6169,10 +6184,10 @@
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="B122" s="4" t="n">
+      <c r="B122" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C122" s="4" t="n">
+      <c r="C122" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -6180,10 +6195,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E122" s="4" t="n">
+      <c r="E122" s="8" t="n">
         <v>19938.2</v>
       </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -6218,10 +6233,10 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="B123" s="4" t="n">
+      <c r="B123" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C123" s="4" t="n">
+      <c r="C123" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -6229,10 +6244,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E123" s="4" t="n">
+      <c r="E123" s="8" t="n">
         <v>23736.3</v>
       </c>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="7" t="n">
         <v>19</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -6267,10 +6282,10 @@
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="B124" s="4" t="n">
+      <c r="B124" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C124" s="4" t="n">
+      <c r="C124" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -6278,10 +6293,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E124" s="4" t="n">
+      <c r="E124" s="8" t="n">
         <v>29921.9</v>
       </c>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -6316,10 +6331,10 @@
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="B125" s="4" t="n">
+      <c r="B125" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C125" s="4" t="n">
+      <c r="C125" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -6327,10 +6342,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E125" s="4" t="n">
+      <c r="E125" s="8" t="n">
         <v>39473.9</v>
       </c>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="8" t="n">
         <v>31.9</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -6365,10 +6380,10 @@
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="B126" s="4" t="n">
+      <c r="B126" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C126" s="4" t="n">
+      <c r="C126" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -6376,10 +6391,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E126" s="4" t="n">
+      <c r="E126" s="7" t="n">
         <v>54611</v>
       </c>
-      <c r="F126" s="4" t="n">
+      <c r="F126" s="8" t="n">
         <v>38.3</v>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -6414,10 +6429,10 @@
           <t>2017-12-01</t>
         </is>
       </c>
-      <c r="B127" s="4" t="n">
+      <c r="B127" s="7" t="n">
         <v>2017</v>
       </c>
-      <c r="C127" s="4" t="n">
+      <c r="C127" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -6425,10 +6440,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E127" s="4" t="n">
+      <c r="E127" s="8" t="n">
         <v>84970.3</v>
       </c>
-      <c r="F127" s="4" t="n">
+      <c r="F127" s="8" t="n">
         <v>55.6</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -6463,10 +6478,10 @@
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n">
+      <c r="B128" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C128" s="4" t="n">
+      <c r="C128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -6474,10 +6489,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E128" s="4" t="n">
+      <c r="E128" s="8" t="n">
         <v>141060.9</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="7" t="n">
         <v>66</v>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -6512,10 +6527,10 @@
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="B129" s="4" t="n">
+      <c r="B129" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C129" s="4" t="n">
+      <c r="C129" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -6523,10 +6538,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E129" s="4" t="n">
+      <c r="E129" s="8" t="n">
         <v>204074.2</v>
       </c>
-      <c r="F129" s="4" t="n">
+      <c r="F129" s="8" t="n">
         <v>44.7</v>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -6561,10 +6576,10 @@
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="B130" s="4" t="n">
+      <c r="B130" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C130" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -6572,10 +6587,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E130" s="4" t="n">
+      <c r="E130" s="8" t="n">
         <v>287622.2</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="8" t="n">
         <v>40.9</v>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -6610,10 +6625,10 @@
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="B131" s="4" t="n">
+      <c r="B131" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C131" s="4" t="n">
+      <c r="C131" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -6621,10 +6636,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E131" s="4" t="n">
+      <c r="E131" s="7" t="n">
         <v>448124</v>
       </c>
-      <c r="F131" s="4" t="n">
+      <c r="F131" s="8" t="n">
         <v>55.8</v>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -6659,10 +6674,10 @@
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="B132" s="4" t="n">
+      <c r="B132" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C132" s="4" t="n">
+      <c r="C132" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -6670,10 +6685,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E132" s="4" t="n">
+      <c r="E132" s="7" t="n">
         <v>942481</v>
       </c>
-      <c r="F132" s="4" t="n">
+      <c r="F132" s="8" t="n">
         <v>110.3</v>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -6708,10 +6723,10 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="B133" s="4" t="n">
+      <c r="B133" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C133" s="4" t="n">
+      <c r="C133" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -6719,10 +6734,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E133" s="4" t="n">
+      <c r="E133" s="8" t="n">
         <v>1853869.6</v>
       </c>
-      <c r="F133" s="4" t="n">
+      <c r="F133" s="8" t="n">
         <v>96.7</v>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6757,10 +6772,10 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="B134" s="4" t="n">
+      <c r="B134" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C134" s="4" t="n">
+      <c r="C134" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -6768,10 +6783,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E134" s="4" t="n">
+      <c r="E134" s="8" t="n">
         <v>3362789.7</v>
       </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="8" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -6806,10 +6821,10 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="B135" s="4" t="n">
+      <c r="B135" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C135" s="4" t="n">
+      <c r="C135" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -6817,10 +6832,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E135" s="4" t="n">
+      <c r="E135" s="8" t="n">
         <v>5919047.9</v>
       </c>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="7" t="n">
         <v>76</v>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6855,10 +6870,10 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="B136" s="4" t="n">
+      <c r="B136" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C136" s="4" t="n">
+      <c r="C136" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -6866,10 +6881,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E136" s="4" t="n">
+      <c r="E136" s="8" t="n">
         <v>13479980.5</v>
       </c>
-      <c r="F136" s="4" t="n">
+      <c r="F136" s="8" t="n">
         <v>127.7</v>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -6904,10 +6919,10 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="B137" s="4" t="n">
+      <c r="B137" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C137" s="4" t="n">
+      <c r="C137" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -6915,10 +6930,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E137" s="4" t="n">
+      <c r="E137" s="8" t="n">
         <v>25355573.7</v>
       </c>
-      <c r="F137" s="4" t="n">
+      <c r="F137" s="8" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -6953,10 +6968,10 @@
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="B138" s="4" t="n">
+      <c r="B138" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C138" s="4" t="n">
+      <c r="C138" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -6964,10 +6979,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E138" s="4" t="n">
+      <c r="E138" s="8" t="n">
         <v>56589583.5</v>
       </c>
-      <c r="F138" s="4" t="n">
+      <c r="F138" s="8" t="n">
         <v>123.2</v>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -7002,10 +7017,10 @@
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="B139" s="4" t="n">
+      <c r="B139" s="7" t="n">
         <v>2018</v>
       </c>
-      <c r="C139" s="4" t="n">
+      <c r="C139" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -7013,10 +7028,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E139" s="4" t="n">
+      <c r="E139" s="8" t="n">
         <v>110597550.2</v>
       </c>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="8" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -7051,10 +7066,10 @@
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="B140" s="4" t="n">
+      <c r="B140" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C140" s="4" t="n">
+      <c r="C140" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -7062,10 +7077,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="E140" s="8" t="n">
         <v>328067725.1</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="8" t="n">
         <v>196.6</v>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -7100,10 +7115,10 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="B141" s="4" t="n">
+      <c r="B141" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C141" s="4" t="n">
+      <c r="C141" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -7111,10 +7126,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E141" s="4" t="n">
+      <c r="E141" s="8" t="n">
         <v>703259098.2</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="F141" s="8" t="n">
         <v>114.4</v>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -7149,10 +7164,10 @@
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="B142" s="4" t="n">
+      <c r="B142" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C142" s="4" t="n">
+      <c r="C142" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -7160,10 +7175,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E142" s="4" t="n">
+      <c r="E142" s="8" t="n">
         <v>948197209.5</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="8" t="n">
         <v>34.8</v>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -7198,10 +7213,10 @@
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="B143" s="4" t="n">
+      <c r="B143" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C143" s="4" t="n">
+      <c r="C143" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -7209,10 +7224,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E143" s="4" t="n">
+      <c r="E143" s="8" t="n">
         <v>1268517190.9</v>
       </c>
-      <c r="F143" s="4" t="n">
+      <c r="F143" s="8" t="n">
         <v>33.8</v>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -7247,10 +7262,10 @@
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="B144" s="4" t="n">
+      <c r="B144" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C144" s="4" t="n">
+      <c r="C144" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -7258,10 +7273,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E144" s="4" t="n">
+      <c r="E144" s="8" t="n">
         <v>1769365833.3</v>
       </c>
-      <c r="F144" s="4" t="n">
+      <c r="F144" s="8" t="n">
         <v>39.5</v>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -7296,10 +7311,10 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="B145" s="4" t="n">
+      <c r="B145" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C145" s="4" t="n">
+      <c r="C145" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -7307,10 +7322,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E145" s="4" t="n">
+      <c r="E145" s="8" t="n">
         <v>2160431069.8</v>
       </c>
-      <c r="F145" s="4" t="n">
+      <c r="F145" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -7345,10 +7360,10 @@
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="B146" s="4" t="n">
+      <c r="B146" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C146" s="4" t="n">
+      <c r="C146" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -7356,10 +7371,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E146" s="4" t="n">
+      <c r="E146" s="8" t="n">
         <v>2579165819.7</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="F146" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -7394,10 +7409,10 @@
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="B147" s="4" t="n">
+      <c r="B147" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C147" s="4" t="n">
+      <c r="C147" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -7405,10 +7420,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E147" s="4" t="n">
+      <c r="E147" s="8" t="n">
         <v>3472176193.2</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="8" t="n">
         <v>34.6</v>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -7443,10 +7458,10 @@
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="B148" s="4" t="n">
+      <c r="B148" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C148" s="4" t="n">
+      <c r="C148" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -7454,10 +7469,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E148" s="4" t="n">
+      <c r="E148" s="8" t="n">
         <v>5286006314.7</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="8" t="n">
         <v>52.2</v>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -7492,10 +7507,10 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="B149" s="4" t="n">
+      <c r="B149" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C149" s="4" t="n">
+      <c r="C149" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -7503,10 +7518,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E149" s="4" t="n">
+      <c r="E149" s="8" t="n">
         <v>6478423619.2</v>
       </c>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -7541,10 +7556,10 @@
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="B150" s="4" t="n">
+      <c r="B150" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C150" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -7552,10 +7567,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E150" s="4" t="n">
+      <c r="E150" s="8" t="n">
         <v>8144026331.7</v>
       </c>
-      <c r="F150" s="4" t="n">
+      <c r="F150" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -7590,10 +7605,10 @@
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="B151" s="4" t="n">
+      <c r="B151" s="7" t="n">
         <v>2019</v>
       </c>
-      <c r="C151" s="4" t="n">
+      <c r="C151" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -7601,10 +7616,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E151" s="4" t="n">
+      <c r="E151" s="8" t="n">
         <v>10711919274.4</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="8" t="n">
         <v>31.5</v>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -7639,10 +7654,10 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="B152" s="4" t="n">
+      <c r="B152" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C152" s="4" t="n">
+      <c r="C152" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -7650,10 +7665,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E152" s="4" t="n">
+      <c r="E152" s="8" t="n">
         <v>17377625281.2</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="8" t="n">
         <v>62.2</v>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -7688,10 +7703,10 @@
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="B153" s="4" t="n">
+      <c r="B153" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C153" s="4" t="n">
+      <c r="C153" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -7699,10 +7714,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E153" s="4" t="n">
+      <c r="E153" s="8" t="n">
         <v>21174462628.9</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="F153" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -7737,10 +7752,10 @@
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="B154" s="4" t="n">
+      <c r="B154" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C154" s="4" t="n">
+      <c r="C154" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -7748,10 +7763,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E154" s="4" t="n">
+      <c r="E154" s="8" t="n">
         <v>23995112795.7</v>
       </c>
-      <c r="F154" s="4" t="n">
+      <c r="F154" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -7786,10 +7801,10 @@
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="B155" s="4" t="n">
+      <c r="B155" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C155" s="4" t="n">
+      <c r="C155" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -7797,10 +7812,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E155" s="4" t="n">
+      <c r="E155" s="8" t="n">
         <v>30594008765.7</v>
       </c>
-      <c r="F155" s="4" t="n">
+      <c r="F155" s="8" t="n">
         <v>27.5</v>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -7835,10 +7850,10 @@
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="B156" s="4" t="n">
+      <c r="B156" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C156" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -7846,10 +7861,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E156" s="4" t="n">
+      <c r="E156" s="8" t="n">
         <v>42404519909.6</v>
       </c>
-      <c r="F156" s="4" t="n">
+      <c r="F156" s="8" t="n">
         <v>38.6</v>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -7884,10 +7899,10 @@
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="B157" s="4" t="n">
+      <c r="B157" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C157" s="4" t="n">
+      <c r="C157" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -7895,10 +7910,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E157" s="4" t="n">
+      <c r="E157" s="8" t="n">
         <v>53033212824.9</v>
       </c>
-      <c r="F157" s="4" t="n">
+      <c r="F157" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -7933,10 +7948,10 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="B158" s="4" t="n">
+      <c r="B158" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C158" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -7944,10 +7959,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E158" s="4" t="n">
+      <c r="E158" s="8" t="n">
         <v>63408630581.9</v>
       </c>
-      <c r="F158" s="4" t="n">
+      <c r="F158" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -7982,10 +7997,10 @@
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="B159" s="4" t="n">
+      <c r="B159" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C159" s="4" t="n">
+      <c r="C159" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -7993,10 +8008,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E159" s="4" t="n">
+      <c r="E159" s="8" t="n">
         <v>79061685127.39999</v>
       </c>
-      <c r="F159" s="4" t="n">
+      <c r="F159" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -8031,10 +8046,10 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="B160" s="4" t="n">
+      <c r="B160" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C160" s="4" t="n">
+      <c r="C160" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -8042,10 +8057,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E160" s="4" t="n">
+      <c r="E160" s="8" t="n">
         <v>101126220212.8</v>
       </c>
-      <c r="F160" s="4" t="n">
+      <c r="F160" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -8080,10 +8095,10 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="B161" s="4" t="n">
+      <c r="B161" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C161" s="4" t="n">
+      <c r="C161" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -8091,10 +8106,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E161" s="4" t="n">
+      <c r="E161" s="8" t="n">
         <v>131945447084.8</v>
       </c>
-      <c r="F161" s="4" t="n">
+      <c r="F161" s="8" t="n">
         <v>30.5</v>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -8129,10 +8144,10 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="B162" s="4" t="n">
+      <c r="B162" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C162" s="4" t="n">
+      <c r="C162" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -8140,10 +8155,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E162" s="4" t="n">
+      <c r="E162" s="8" t="n">
         <v>184682722830.1</v>
       </c>
-      <c r="F162" s="4" t="n">
+      <c r="F162" s="7" t="n">
         <v>40</v>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -8178,10 +8193,10 @@
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="B163" s="4" t="n">
+      <c r="B163" s="7" t="n">
         <v>2020</v>
       </c>
-      <c r="C163" s="4" t="n">
+      <c r="C163" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -8189,10 +8204,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E163" s="4" t="n">
+      <c r="E163" s="7" t="n">
         <v>327767509170</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="F163" s="8" t="n">
         <v>77.5</v>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -8227,10 +8242,10 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="B164" s="4" t="n">
+      <c r="B164" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C164" s="4" t="n">
+      <c r="C164" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -8238,10 +8253,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E164" s="4" t="n">
+      <c r="E164" s="8" t="n">
         <v>480553055894.4</v>
       </c>
-      <c r="F164" s="4" t="n">
+      <c r="F164" s="8" t="n">
         <v>46.6</v>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -8276,10 +8291,10 @@
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="B165" s="4" t="n">
+      <c r="B165" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C165" s="4" t="n">
+      <c r="C165" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -8287,10 +8302,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E165" s="4" t="n">
+      <c r="E165" s="8" t="n">
         <v>643008821970.1</v>
       </c>
-      <c r="F165" s="4" t="n">
+      <c r="F165" s="8" t="n">
         <v>33.8</v>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -8325,10 +8340,10 @@
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="B166" s="4" t="n">
+      <c r="B166" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C166" s="4" t="n">
+      <c r="C166" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -8336,10 +8351,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E166" s="4" t="n">
+      <c r="E166" s="8" t="n">
         <v>746784015747.9</v>
       </c>
-      <c r="F166" s="4" t="n">
+      <c r="F166" s="8" t="n">
         <v>16.1</v>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -8374,10 +8389,10 @@
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="B167" s="4" t="n">
+      <c r="B167" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C167" s="4" t="n">
+      <c r="C167" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -8385,10 +8400,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E167" s="4" t="n">
+      <c r="E167" s="8" t="n">
         <v>930306187617.9</v>
       </c>
-      <c r="F167" s="4" t="n">
+      <c r="F167" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -8423,10 +8438,10 @@
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="B168" s="4" t="n">
+      <c r="B168" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C168" s="4" t="n">
+      <c r="C168" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -8434,10 +8449,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E168" s="4" t="n">
+      <c r="E168" s="8" t="n">
         <v>1195582997017.2</v>
       </c>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="8" t="n">
         <v>28.5</v>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -8472,10 +8487,10 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="B169" s="4" t="n">
+      <c r="B169" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C169" s="4" t="n">
+      <c r="C169" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -8483,10 +8498,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E169" s="4" t="n">
+      <c r="E169" s="8" t="n">
         <v>1383038455119.5</v>
       </c>
-      <c r="F169" s="4" t="n">
+      <c r="F169" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -8521,10 +8536,10 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="B170" s="4" t="n">
+      <c r="B170" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C170" s="4" t="n">
+      <c r="C170" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -8532,10 +8547,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E170" s="4" t="n">
+      <c r="E170" s="8" t="n">
         <v>1613383509819.7</v>
       </c>
-      <c r="F170" s="4" t="n">
+      <c r="F170" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -8570,10 +8585,10 @@
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="B171" s="4" t="n">
+      <c r="B171" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C171" s="4" t="n">
+      <c r="C171" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -8581,10 +8596,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E171" s="4" t="n">
+      <c r="E171" s="8" t="n">
         <v>1932171957524.9</v>
       </c>
-      <c r="F171" s="4" t="n">
+      <c r="F171" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -8619,10 +8634,10 @@
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="B172" s="4" t="n">
+      <c r="B172" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C172" s="4" t="n">
+      <c r="C172" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -8630,10 +8645,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E172" s="4" t="n">
+      <c r="E172" s="8" t="n">
         <v>2069027697276.4</v>
       </c>
-      <c r="F172" s="4" t="n">
+      <c r="F172" s="8" t="n">
         <v>7.1</v>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -8668,10 +8683,10 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="B173" s="4" t="n">
+      <c r="B173" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C173" s="4" t="n">
+      <c r="C173" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -8679,10 +8694,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E173" s="4" t="n">
+      <c r="E173" s="8" t="n">
         <v>2210425050108.3</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="F173" s="8" t="n">
         <v>6.8</v>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -8717,10 +8732,10 @@
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="B174" s="4" t="n">
+      <c r="B174" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C174" s="4" t="n">
+      <c r="C174" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -8728,10 +8743,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E174" s="4" t="n">
+      <c r="E174" s="8" t="n">
         <v>2396255484070.9</v>
       </c>
-      <c r="F174" s="4" t="n">
+      <c r="F174" s="8" t="n">
         <v>8.4</v>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -8766,10 +8781,10 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="B175" s="4" t="n">
+      <c r="B175" s="7" t="n">
         <v>2021</v>
       </c>
-      <c r="C175" s="4" t="n">
+      <c r="C175" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -8777,10 +8792,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E175" s="4" t="n">
+      <c r="E175" s="7" t="n">
         <v>2577508248886</v>
       </c>
-      <c r="F175" s="4" t="n">
+      <c r="F175" s="8" t="n">
         <v>7.6</v>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -8815,10 +8830,10 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="B176" s="4" t="n">
+      <c r="B176" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C176" s="4" t="n">
+      <c r="C176" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -8826,10 +8841,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E176" s="4" t="n">
+      <c r="E176" s="7" t="n">
         <v>2750974554036</v>
       </c>
-      <c r="F176" s="4" t="n">
+      <c r="F176" s="8" t="n">
         <v>6.7</v>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -8864,10 +8879,10 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="B177" s="4" t="n">
+      <c r="B177" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C177" s="4" t="n">
+      <c r="C177" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -8875,10 +8890,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E177" s="4" t="n">
+      <c r="E177" s="8" t="n">
         <v>2832100793634.5</v>
       </c>
-      <c r="F177" s="4" t="n">
+      <c r="F177" s="8" t="n">
         <v>2.9</v>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -8913,10 +8928,10 @@
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="B178" s="4" t="n">
+      <c r="B178" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C178" s="4" t="n">
+      <c r="C178" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -8924,10 +8939,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E178" s="4" t="n">
+      <c r="E178" s="8" t="n">
         <v>2870702327451.8</v>
       </c>
-      <c r="F178" s="4" t="n">
+      <c r="F178" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -8962,10 +8977,10 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="B179" s="4" t="n">
+      <c r="B179" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C179" s="4" t="n">
+      <c r="C179" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -8973,10 +8988,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E179" s="4" t="n">
+      <c r="E179" s="8" t="n">
         <v>2997960561627.7</v>
       </c>
-      <c r="F179" s="4" t="n">
+      <c r="F179" s="8" t="n">
         <v>4.4</v>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -9011,10 +9026,10 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="B180" s="4" t="n">
+      <c r="B180" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C180" s="4" t="n">
+      <c r="C180" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -9022,10 +9037,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E180" s="4" t="n">
+      <c r="E180" s="8" t="n">
         <v>3194057161963.8</v>
       </c>
-      <c r="F180" s="4" t="n">
+      <c r="F180" s="8" t="n">
         <v>6.5</v>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -9060,10 +9075,10 @@
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="B181" s="4" t="n">
+      <c r="B181" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C181" s="4" t="n">
+      <c r="C181" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -9071,10 +9086,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E181" s="4" t="n">
+      <c r="E181" s="8" t="n">
         <v>3557760912588.8</v>
       </c>
-      <c r="F181" s="4" t="n">
+      <c r="F181" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -9109,10 +9124,10 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="B182" s="4" t="n">
+      <c r="B182" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C182" s="4" t="n">
+      <c r="C182" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -9120,10 +9135,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E182" s="4" t="n">
+      <c r="E182" s="8" t="n">
         <v>3825157521197.5</v>
       </c>
-      <c r="F182" s="4" t="n">
+      <c r="F182" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -9158,10 +9173,10 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="B183" s="4" t="n">
+      <c r="B183" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C183" s="4" t="n">
+      <c r="C183" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -9169,10 +9184,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E183" s="4" t="n">
+      <c r="E183" s="8" t="n">
         <v>4137433044225.2</v>
       </c>
-      <c r="F183" s="4" t="n">
+      <c r="F183" s="8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -9207,10 +9222,10 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="B184" s="4" t="n">
+      <c r="B184" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C184" s="4" t="n">
+      <c r="C184" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -9218,10 +9233,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E184" s="4" t="n">
+      <c r="E184" s="8" t="n">
         <v>5326371620985.8</v>
       </c>
-      <c r="F184" s="4" t="n">
+      <c r="F184" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -9256,10 +9271,10 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="B185" s="4" t="n">
+      <c r="B185" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C185" s="4" t="n">
+      <c r="C185" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -9267,10 +9282,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E185" s="4" t="n">
+      <c r="E185" s="8" t="n">
         <v>5654207045137.4</v>
       </c>
-      <c r="F185" s="4" t="n">
+      <c r="F185" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -9305,10 +9320,10 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="B186" s="4" t="n">
+      <c r="B186" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C186" s="4" t="n">
+      <c r="C186" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -9316,10 +9331,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E186" s="4" t="n">
+      <c r="E186" s="8" t="n">
         <v>6364445508067.7</v>
       </c>
-      <c r="F186" s="4" t="n">
+      <c r="F186" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -9354,10 +9369,10 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="B187" s="4" t="n">
+      <c r="B187" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="C187" s="4" t="n">
+      <c r="C187" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -9365,10 +9380,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E187" s="4" t="n">
+      <c r="E187" s="8" t="n">
         <v>8610897384090.4</v>
       </c>
-      <c r="F187" s="4" t="n">
+      <c r="F187" s="8" t="n">
         <v>35.3</v>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -9403,10 +9418,10 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="B188" s="4" t="n">
+      <c r="B188" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C188" s="4" t="n">
+      <c r="C188" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -9414,10 +9429,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E188" s="4" t="n">
+      <c r="E188" s="8" t="n">
         <v>12239280550707.2</v>
       </c>
-      <c r="F188" s="4" t="n">
+      <c r="F188" s="8" t="n">
         <v>42.1</v>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -9452,10 +9467,10 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B189" s="4" t="n">
+      <c r="B189" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C189" s="4" t="n">
+      <c r="C189" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -9463,10 +9478,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E189" s="4" t="n">
+      <c r="E189" s="8" t="n">
         <v>14601356012641.3</v>
       </c>
-      <c r="F189" s="4" t="n">
+      <c r="F189" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -9501,10 +9516,10 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="B190" s="4" t="n">
+      <c r="B190" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C190" s="4" t="n">
+      <c r="C190" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -9512,10 +9527,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E190" s="4" t="n">
+      <c r="E190" s="8" t="n">
         <v>15490514782940.4</v>
       </c>
-      <c r="F190" s="4" t="n">
+      <c r="F190" s="8" t="n">
         <v>6.1</v>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -9550,10 +9565,10 @@
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="B191" s="4" t="n">
+      <c r="B191" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C191" s="4" t="n">
+      <c r="C191" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -9561,10 +9576,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E191" s="4" t="n">
+      <c r="E191" s="7" t="n">
         <v>16079339845626</v>
       </c>
-      <c r="F191" s="4" t="n">
+      <c r="F191" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -9599,10 +9614,10 @@
           <t>2023-05-01</t>
         </is>
       </c>
-      <c r="B192" s="4" t="n">
+      <c r="B192" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C192" s="4" t="n">
+      <c r="C192" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -9610,10 +9625,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E192" s="4" t="n">
+      <c r="E192" s="8" t="n">
         <v>16903293865395.6</v>
       </c>
-      <c r="F192" s="4" t="n">
+      <c r="F192" s="8" t="n">
         <v>5.1</v>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -9648,10 +9663,10 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="B193" s="4" t="n">
+      <c r="B193" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C193" s="4" t="n">
+      <c r="C193" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -9659,10 +9674,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E193" s="4" t="n">
+      <c r="E193" s="8" t="n">
         <v>17944103145979.7</v>
       </c>
-      <c r="F193" s="4" t="n">
+      <c r="F193" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -9697,10 +9712,10 @@
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="B194" s="4" t="n">
+      <c r="B194" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C194" s="4" t="n">
+      <c r="C194" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -9708,10 +9723,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E194" s="4" t="n">
+      <c r="E194" s="8" t="n">
         <v>19056534940064.7</v>
       </c>
-      <c r="F194" s="4" t="n">
+      <c r="F194" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -9746,10 +9761,10 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="B195" s="4" t="n">
+      <c r="B195" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C195" s="4" t="n">
+      <c r="C195" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -9757,10 +9772,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E195" s="4" t="n">
+      <c r="E195" s="8" t="n">
         <v>20470345755220.7</v>
       </c>
-      <c r="F195" s="4" t="n">
+      <c r="F195" s="8" t="n">
         <v>7.4</v>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -9795,10 +9810,10 @@
           <t>2023-09-01</t>
         </is>
       </c>
-      <c r="B196" s="4" t="n">
+      <c r="B196" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C196" s="4" t="n">
+      <c r="C196" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -9806,10 +9821,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E196" s="4" t="n">
+      <c r="E196" s="8" t="n">
         <v>22244633245832.3</v>
       </c>
-      <c r="F196" s="4" t="n">
+      <c r="F196" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -9844,10 +9859,10 @@
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="B197" s="4" t="n">
+      <c r="B197" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C197" s="4" t="n">
+      <c r="C197" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -9855,10 +9870,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E197" s="4" t="n">
+      <c r="E197" s="8" t="n">
         <v>23547066398042.6</v>
       </c>
-      <c r="F197" s="4" t="n">
+      <c r="F197" s="8" t="n">
         <v>5.9</v>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -9893,10 +9908,10 @@
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="B198" s="4" t="n">
+      <c r="B198" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C198" s="4" t="n">
+      <c r="C198" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -9904,10 +9919,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E198" s="4" t="n">
+      <c r="E198" s="8" t="n">
         <v>24361617825691.9</v>
       </c>
-      <c r="F198" s="4" t="n">
+      <c r="F198" s="8" t="n">
         <v>3.5</v>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -9942,10 +9957,10 @@
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="B199" s="4" t="n">
+      <c r="B199" s="7" t="n">
         <v>2023</v>
       </c>
-      <c r="C199" s="4" t="n">
+      <c r="C199" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -9953,10 +9968,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E199" s="4" t="n">
+      <c r="E199" s="8" t="n">
         <v>24952896762695.5</v>
       </c>
-      <c r="F199" s="4" t="n">
+      <c r="F199" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -9991,10 +10006,10 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="B200" s="4" t="n">
+      <c r="B200" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C200" s="4" t="n">
+      <c r="C200" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -10002,10 +10017,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E200" s="4" t="n">
+      <c r="E200" s="8" t="n">
         <v>25379624724721.4</v>
       </c>
-      <c r="F200" s="4" t="n">
+      <c r="F200" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -10040,10 +10055,10 @@
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="B201" s="4" t="n">
+      <c r="B201" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C201" s="4" t="n">
+      <c r="C201" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -10051,10 +10066,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E201" s="4" t="n">
+      <c r="E201" s="8" t="n">
         <v>25684975429035.5</v>
       </c>
-      <c r="F201" s="4" t="n">
+      <c r="F201" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -10089,10 +10104,10 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="B202" s="4" t="n">
+      <c r="B202" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C202" s="4" t="n">
+      <c r="C202" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -10100,10 +10115,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E202" s="4" t="n">
+      <c r="E202" s="8" t="n">
         <v>25986417377849.1</v>
       </c>
-      <c r="F202" s="4" t="n">
+      <c r="F202" s="8" t="n">
         <v>1.2</v>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -10138,10 +10153,10 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="B203" s="4" t="n">
+      <c r="B203" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C203" s="4" t="n">
+      <c r="C203" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -10149,10 +10164,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E203" s="4" t="n">
+      <c r="E203" s="8" t="n">
         <v>26516834159241.7</v>
       </c>
-      <c r="F203" s="4" t="n">
+      <c r="F203" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -10187,10 +10202,10 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="B204" s="4" t="n">
+      <c r="B204" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C204" s="4" t="n">
+      <c r="C204" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -10198,10 +10213,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E204" s="4" t="n">
+      <c r="E204" s="8" t="n">
         <v>26903972496868.1</v>
       </c>
-      <c r="F204" s="4" t="n">
+      <c r="F204" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -10236,10 +10251,10 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="B205" s="4" t="n">
+      <c r="B205" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C205" s="4" t="n">
+      <c r="C205" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -10247,10 +10262,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E205" s="4" t="n">
+      <c r="E205" s="8" t="n">
         <v>27162536873498.1</v>
       </c>
-      <c r="F205" s="4" t="n">
+      <c r="F205" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -10285,10 +10300,10 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="B206" s="4" t="n">
+      <c r="B206" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C206" s="4" t="n">
+      <c r="C206" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -10296,10 +10311,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E206" s="4" t="n">
+      <c r="E206" s="8" t="n">
         <v>27366064708317.6</v>
       </c>
-      <c r="F206" s="4" t="n">
+      <c r="F206" s="8" t="n">
         <v>0.7</v>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -10334,10 +10349,10 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="B207" s="4" t="n">
+      <c r="B207" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C207" s="4" t="n">
+      <c r="C207" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -10345,10 +10360,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E207" s="4" t="n">
+      <c r="E207" s="8" t="n">
         <v>27746667522384.2</v>
       </c>
-      <c r="F207" s="4" t="n">
+      <c r="F207" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -10383,10 +10398,10 @@
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B208" s="4" t="n">
+      <c r="B208" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C208" s="4" t="n">
+      <c r="C208" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -10394,10 +10409,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E208" s="4" t="n">
+      <c r="E208" s="8" t="n">
         <v>27972976631499.6</v>
       </c>
-      <c r="F208" s="4" t="n">
+      <c r="F208" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -10432,10 +10447,10 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="B209" s="4" t="n">
+      <c r="B209" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C209" s="4" t="n">
+      <c r="C209" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -10443,10 +10458,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E209" s="4" t="n">
+      <c r="E209" s="8" t="n">
         <v>29100339690082.1</v>
       </c>
-      <c r="F209" s="4" t="n">
+      <c r="F209" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -10481,10 +10496,10 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="B210" s="4" t="n">
+      <c r="B210" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C210" s="4" t="n">
+      <c r="C210" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -10492,10 +10507,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E210" s="4" t="n">
+      <c r="E210" s="8" t="n">
         <v>33516689669759.1</v>
       </c>
-      <c r="F210" s="4" t="n">
+      <c r="F210" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -10530,10 +10545,10 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="B211" s="4" t="n">
+      <c r="B211" s="7" t="n">
         <v>2024</v>
       </c>
-      <c r="C211" s="4" t="n">
+      <c r="C211" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -10541,10 +10556,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E211" s="4" t="n">
+      <c r="E211" s="8" t="n">
         <v>36919909673224.9</v>
       </c>
-      <c r="F211" s="4" t="n">
+      <c r="F211" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -10579,10 +10594,10 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="B212" s="4" t="n">
+      <c r="B212" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C212" s="4" t="n">
+      <c r="C212" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -10590,10 +10605,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E212" s="4" t="n">
+      <c r="E212" s="8" t="n">
         <v>40521840708458.3</v>
       </c>
-      <c r="F212" s="4" t="n">
+      <c r="F212" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -10628,10 +10643,10 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="B213" s="4" t="n">
+      <c r="B213" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C213" s="4" t="n">
+      <c r="C213" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -10639,10 +10654,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E213" s="4" t="n">
+      <c r="E213" s="8" t="n">
         <v>44948592993158.4</v>
       </c>
-      <c r="F213" s="4" t="n">
+      <c r="F213" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -10677,10 +10692,10 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="B214" s="4" t="n">
+      <c r="B214" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C214" s="4" t="n">
+      <c r="C214" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -10688,10 +10703,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E214" s="4" t="n">
+      <c r="E214" s="8" t="n">
         <v>48695941027700.9</v>
       </c>
-      <c r="F214" s="4" t="n">
+      <c r="F214" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -10726,10 +10741,10 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B215" s="4" t="n">
+      <c r="B215" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C215" s="4" t="n">
+      <c r="C215" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -10737,10 +10752,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E215" s="4" t="n">
+      <c r="E215" s="8" t="n">
         <v>56686369544411.3</v>
       </c>
-      <c r="F215" s="4" t="n">
+      <c r="F215" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -10775,10 +10790,10 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B216" s="4" t="n">
+      <c r="B216" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C216" s="4" t="n">
+      <c r="C216" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -10786,10 +10801,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E216" s="4" t="n">
+      <c r="E216" s="8" t="n">
         <v>68691300824090.4</v>
       </c>
-      <c r="F216" s="4" t="n">
+      <c r="F216" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -10824,10 +10839,10 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="B217" s="4" t="n">
+      <c r="B217" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C217" s="4" t="n">
+      <c r="C217" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -10835,10 +10850,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E217" s="4" t="n">
+      <c r="E217" s="8" t="n">
         <v>75780386243945.11</v>
       </c>
-      <c r="F217" s="4" t="n">
+      <c r="F217" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -10873,10 +10888,10 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="B218" s="4" t="n">
+      <c r="B218" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C218" s="4" t="n">
+      <c r="C218" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -10884,10 +10899,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E218" s="4" t="n">
+      <c r="E218" s="8" t="n">
         <v>86578516564082.41</v>
       </c>
-      <c r="F218" s="4" t="n">
+      <c r="F218" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -10922,10 +10937,10 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="B219" s="4" t="n">
+      <c r="B219" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C219" s="4" t="n">
+      <c r="C219" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -10933,10 +10948,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E219" s="4" t="n">
+      <c r="E219" s="7" t="n">
         <v>100503985890336</v>
       </c>
-      <c r="F219" s="4" t="n">
+      <c r="F219" s="8" t="n">
         <v>16.1</v>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -10971,10 +10986,10 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="B220" s="4" t="n">
+      <c r="B220" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C220" s="4" t="n">
+      <c r="C220" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -10982,10 +10997,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E220" s="4" t="n">
+      <c r="E220" s="7" t="n">
         <v>122169616603139</v>
       </c>
-      <c r="F220" s="4" t="n">
+      <c r="F220" s="8" t="n">
         <v>21.55698654224845</v>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -11020,10 +11035,10 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B221" s="4" t="n">
+      <c r="B221" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C221" s="4" t="n">
+      <c r="C221" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -11031,10 +11046,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E221" s="4" t="n">
+      <c r="E221" s="7" t="n">
         <v>153849788402697</v>
       </c>
-      <c r="F221" s="4" t="n">
+      <c r="F221" s="8" t="n">
         <v>25.93130164472011</v>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -11069,10 +11084,10 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="B222" s="4" t="n">
+      <c r="B222" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C222" s="4" t="n">
+      <c r="C222" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -11080,10 +11095,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E222" s="4" t="n">
+      <c r="E222" s="7" t="n">
         <v>187021825372618</v>
       </c>
-      <c r="F222" s="4" t="n">
+      <c r="F222" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -11118,10 +11133,10 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B223" s="4" t="n">
+      <c r="B223" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="C223" s="4" t="n">
+      <c r="C223" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -11129,10 +11144,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E223" s="4" t="n">
+      <c r="E223" s="7" t="n">
         <v>212393273459827</v>
       </c>
-      <c r="F223" s="4" t="n">
+      <c r="F223" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -11167,10 +11182,10 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B224" s="4" t="n">
+      <c r="B224" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="C224" s="4" t="n">
+      <c r="C224" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -11178,10 +11193,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E224" s="4" t="n">
+      <c r="E224" s="7" t="n">
         <v>281565112063483</v>
       </c>
-      <c r="F224" s="4" t="n">
+      <c r="F224" s="8" t="n">
         <v>32.6</v>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -11216,10 +11231,10 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B225" s="4" t="n">
+      <c r="B225" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="C225" s="4" t="n">
+      <c r="C225" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -11227,10 +11242,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E225" s="4" t="n">
+      <c r="E225" s="7" t="n">
         <v>322703709401564</v>
       </c>
-      <c r="F225" s="4" t="n">
+      <c r="F225" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -11265,10 +11280,10 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="B226" s="4" t="n">
+      <c r="B226" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="C226" s="4" t="n">
+      <c r="C226" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -11276,10 +11291,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E226" s="4" t="n">
+      <c r="E226" s="7" t="n">
         <v>364960489482614</v>
       </c>
-      <c r="F226" s="4" t="n">
+      <c r="F226" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -11314,10 +11329,10 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B227" s="4" t="n">
+      <c r="B227" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="C227" s="4" t="n">
+      <c r="C227" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -11325,10 +11340,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E227" s="4" t="n">
+      <c r="E227" s="7" t="n">
         <v>403528566746262</v>
       </c>
-      <c r="F227" s="4" t="n">
+      <c r="F227" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -11363,10 +11378,10 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B228" s="4" t="n">
+      <c r="B228" s="7" t="n">
         <v>2026</v>
       </c>
-      <c r="C228" s="4" t="n">
+      <c r="C228" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -11374,10 +11389,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E228" s="4" t="n">
+      <c r="E228" s="8" t="n">
         <v>428967191622142.1</v>
       </c>
-      <c r="F228" s="4" t="n">
+      <c r="F228" s="8" t="n">
         <v>6.3</v>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -11568,7 +11583,7 @@
           <t>records</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="7" t="n">
         <v>222</v>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -491,57 +491,57 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>Año</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>month_name</t>
+          <t>Nombre del mes</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>index_value</t>
+          <t>Valor del índice</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>monthly_variation_pct</t>
+          <t>Variación mensual (%)</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Unidad</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>Frecuencia</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Fuente</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>URL fuente</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>fetched_at</t>
+          <t>Fecha de captura</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,26 +82,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -455,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K228"/>
+  <dimension ref="A1:K229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -551,10 +613,10 @@
           <t>2007-12-01</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="5" t="n">
         <v>2007</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -562,7 +624,7 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="5" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="4" t="n"/>
@@ -588,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -598,10 +660,10 @@
           <t>2008-01-01</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -609,10 +671,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="6" t="n">
         <v>103.1</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="6" t="n">
         <v>3.1</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -637,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -647,10 +709,10 @@
           <t>2008-02-01</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -658,10 +720,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="6" t="n">
         <v>105.3</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -686,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -696,10 +758,10 @@
           <t>2008-03-01</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -707,10 +769,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="6" t="n">
         <v>107.1</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -735,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -745,10 +807,10 @@
           <t>2008-04-01</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -756,10 +818,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="6" t="n">
         <v>108.9</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -784,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -794,10 +856,10 @@
           <t>2008-05-01</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -805,10 +867,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="6" t="n">
         <v>112.4</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -833,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -843,10 +905,10 @@
           <t>2008-06-01</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -854,10 +916,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="6" t="n">
         <v>115.1</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="6" t="n">
         <v>2.4</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -882,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -892,10 +954,10 @@
           <t>2008-07-01</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -903,10 +965,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="6" t="n">
         <v>117.3</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -931,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -941,10 +1003,10 @@
           <t>2008-08-01</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -952,10 +1014,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="6" t="n">
         <v>119.4</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -980,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -990,10 +1052,10 @@
           <t>2008-09-01</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1001,10 +1063,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="6" t="n">
         <v>121.8</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1029,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1039,10 +1101,10 @@
           <t>2008-10-01</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1050,10 +1112,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="6" t="n">
         <v>124.7</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="6" t="n">
         <v>2.4</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1078,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1088,10 +1150,10 @@
           <t>2008-11-01</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1099,10 +1161,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="6" t="n">
         <v>127.6</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="6" t="n">
         <v>2.3</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1127,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1137,10 +1199,10 @@
           <t>2008-12-01</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1148,10 +1210,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="6" t="n">
         <v>130.9</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="6" t="n">
         <v>2.6</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1176,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1186,10 +1248,10 @@
           <t>2009-01-01</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1197,10 +1259,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="6" t="n">
         <v>133.9</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="6" t="n">
         <v>2.3</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1225,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1235,10 +1297,10 @@
           <t>2009-02-01</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1246,10 +1308,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="6" t="n">
         <v>135.6</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="6" t="n">
         <v>1.3</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1274,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1284,10 +1346,10 @@
           <t>2009-03-01</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1295,10 +1357,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="6" t="n">
         <v>137.2</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="6" t="n">
         <v>1.2</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1323,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1333,10 +1395,10 @@
           <t>2009-04-01</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1344,10 +1406,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="6" t="n">
         <v>139.7</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1372,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1382,10 +1444,10 @@
           <t>2009-05-01</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B24" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1393,10 +1455,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="6" t="n">
         <v>142.5</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1421,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1431,10 +1493,10 @@
           <t>2009-06-01</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1442,10 +1504,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1470,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1480,10 +1542,10 @@
           <t>2009-07-01</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
+      <c r="B26" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1491,10 +1553,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1519,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1529,10 +1591,10 @@
           <t>2009-08-01</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1540,10 +1602,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="6" t="n">
         <v>151.3</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1568,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1578,10 +1640,10 @@
           <t>2009-09-01</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B28" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1589,10 +1651,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="6" t="n">
         <v>155.1</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1617,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1627,10 +1689,10 @@
           <t>2009-10-01</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1638,10 +1700,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="5" t="n">
         <v>158</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1666,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1676,10 +1738,10 @@
           <t>2009-11-01</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
+      <c r="B30" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1687,10 +1749,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="5" t="n">
         <v>161</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1715,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1725,10 +1787,10 @@
           <t>2009-12-01</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1736,10 +1798,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="6" t="n">
         <v>163.7</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -1764,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1774,10 +1836,10 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
+      <c r="B32" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1785,10 +1847,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="6" t="n">
         <v>166.5</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -1813,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1823,10 +1885,10 @@
           <t>2010-02-01</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1834,10 +1896,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="6" t="n">
         <v>169.1</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -1862,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1872,10 +1934,10 @@
           <t>2010-03-01</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
+      <c r="B34" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1883,10 +1945,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="6" t="n">
         <v>173.2</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="6" t="n">
         <v>2.4</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -1911,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1983,10 @@
           <t>2010-04-01</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1932,10 +1994,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="6" t="n">
         <v>182.2</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="6" t="n">
         <v>5.2</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -1960,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -1970,10 +2032,10 @@
           <t>2010-05-01</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n">
+      <c r="B36" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1981,10 +2043,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="5" t="n">
         <v>187</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="6" t="n">
         <v>2.6</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2009,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2019,10 +2081,10 @@
           <t>2010-06-01</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2030,10 +2092,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="6" t="n">
         <v>190.4</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2058,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2068,10 +2130,10 @@
           <t>2010-07-01</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B38" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2079,10 +2141,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="6" t="n">
         <v>193.1</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2107,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2117,10 +2179,10 @@
           <t>2010-08-01</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2128,10 +2190,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="6" t="n">
         <v>196.2</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2156,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2228,10 @@
           <t>2010-09-01</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B40" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2177,10 +2239,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="6" t="n">
         <v>198.4</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2205,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2215,10 +2277,10 @@
           <t>2010-10-01</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B41" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2226,10 +2288,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="6" t="n">
         <v>201.4</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2254,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2264,10 +2326,10 @@
           <t>2010-11-01</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B42" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2275,10 +2337,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="6" t="n">
         <v>204.5</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2303,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2313,10 +2375,10 @@
           <t>2010-12-01</t>
         </is>
       </c>
-      <c r="B43" s="7" t="n">
+      <c r="B43" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2324,10 +2386,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="6" t="n">
         <v>208.2</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2352,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2362,10 +2424,10 @@
           <t>2011-01-01</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n">
+      <c r="B44" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2373,10 +2435,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="6" t="n">
         <v>213.9</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="6" t="n">
         <v>2.7</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2401,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2411,10 +2473,10 @@
           <t>2011-02-01</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n">
+      <c r="B45" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2422,10 +2484,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" s="6" t="n">
         <v>217.6</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2450,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2460,10 +2522,10 @@
           <t>2011-03-01</t>
         </is>
       </c>
-      <c r="B46" s="7" t="n">
+      <c r="B46" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2471,10 +2533,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E46" s="8" t="n">
+      <c r="E46" s="6" t="n">
         <v>220.7</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2499,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2571,10 @@
           <t>2011-04-01</t>
         </is>
       </c>
-      <c r="B47" s="7" t="n">
+      <c r="B47" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2520,10 +2582,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" s="6" t="n">
         <v>223.9</v>
       </c>
-      <c r="F47" s="8" t="n">
+      <c r="F47" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -2548,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2558,10 +2620,10 @@
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n">
+      <c r="B48" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2569,10 +2631,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E48" s="6" t="n">
         <v>229.6</v>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="F48" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -2597,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2607,10 +2669,10 @@
           <t>2011-06-01</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n">
+      <c r="B49" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2618,10 +2680,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="E49" s="6" t="n">
         <v>235.3</v>
       </c>
-      <c r="F49" s="8" t="n">
+      <c r="F49" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -2646,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2656,10 +2718,10 @@
           <t>2011-07-01</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n">
+      <c r="B50" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2667,10 +2729,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E50" s="6" t="n">
         <v>241.6</v>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="F50" s="6" t="n">
         <v>2.7</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -2695,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2705,10 +2767,10 @@
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n">
+      <c r="B51" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2716,10 +2778,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="E51" s="6" t="n">
         <v>246.9</v>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="F51" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2744,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2754,10 +2816,10 @@
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="B52" s="7" t="n">
+      <c r="B52" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2765,10 +2827,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="E52" s="6" t="n">
         <v>250.9</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2793,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2803,10 +2865,10 @@
           <t>2011-10-01</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B53" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2814,10 +2876,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E53" s="6" t="n">
         <v>255.5</v>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2842,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2852,10 +2914,10 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n">
+      <c r="B54" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2863,10 +2925,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n">
+      <c r="E54" s="5" t="n">
         <v>261</v>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="F54" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2891,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2901,10 +2963,10 @@
           <t>2011-12-01</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n">
+      <c r="B55" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2912,10 +2974,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E55" s="8" t="n">
+      <c r="E55" s="6" t="n">
         <v>265.6</v>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -2940,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2950,10 +3012,10 @@
           <t>2012-01-01</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n">
+      <c r="B56" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2961,10 +3023,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E56" s="8" t="n">
+      <c r="E56" s="6" t="n">
         <v>269.6</v>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F56" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -2989,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -2999,10 +3061,10 @@
           <t>2012-02-01</t>
         </is>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3010,10 +3072,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E57" s="8" t="n">
+      <c r="E57" s="6" t="n">
         <v>272.6</v>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="F57" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3038,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3048,10 +3110,10 @@
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="B58" s="7" t="n">
+      <c r="B58" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3059,10 +3121,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n">
+      <c r="E58" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="F58" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3087,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3097,10 +3159,10 @@
           <t>2012-04-01</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B59" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3108,10 +3170,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E59" s="8" t="n">
+      <c r="E59" s="6" t="n">
         <v>277.2</v>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="F59" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3136,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3208,10 @@
           <t>2012-05-01</t>
         </is>
       </c>
-      <c r="B60" s="7" t="n">
+      <c r="B60" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3157,10 +3219,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E60" s="8" t="n">
+      <c r="E60" s="6" t="n">
         <v>281.5</v>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3185,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3195,10 +3257,10 @@
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n">
+      <c r="B61" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3206,10 +3268,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E61" s="8" t="n">
+      <c r="E61" s="6" t="n">
         <v>285.5</v>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="F61" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3234,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3244,10 +3306,10 @@
           <t>2012-07-01</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n">
+      <c r="B62" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3255,10 +3317,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E62" s="8" t="n">
+      <c r="E62" s="6" t="n">
         <v>288.4</v>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F62" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3283,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3293,10 +3355,10 @@
           <t>2012-08-01</t>
         </is>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B63" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3304,10 +3366,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E63" s="8" t="n">
+      <c r="E63" s="6" t="n">
         <v>291.5</v>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="F63" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -3332,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3342,10 +3404,10 @@
           <t>2012-09-01</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n">
+      <c r="B64" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3353,10 +3415,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E64" s="8" t="n">
+      <c r="E64" s="6" t="n">
         <v>296.1</v>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="F64" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -3381,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3391,10 +3453,10 @@
           <t>2012-10-01</t>
         </is>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B65" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3402,10 +3464,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E65" s="6" t="n">
         <v>301.2</v>
       </c>
-      <c r="F65" s="8" t="n">
+      <c r="F65" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3430,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3440,10 +3502,10 @@
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n">
+      <c r="B66" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3451,10 +3513,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E66" s="8" t="n">
+      <c r="E66" s="6" t="n">
         <v>308.1</v>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="F66" s="6" t="n">
         <v>2.3</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -3479,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3489,10 +3551,10 @@
           <t>2012-12-01</t>
         </is>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3500,10 +3562,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E67" s="8" t="n">
+      <c r="E67" s="6" t="n">
         <v>318.9</v>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3528,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3538,10 +3600,10 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
+      <c r="B68" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3549,10 +3611,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="E68" s="6" t="n">
         <v>329.4</v>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="F68" s="6" t="n">
         <v>3.3</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -3577,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3587,10 +3649,10 @@
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="B69" s="7" t="n">
+      <c r="B69" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C69" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3598,10 +3660,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E69" s="8" t="n">
+      <c r="E69" s="6" t="n">
         <v>334.8</v>
       </c>
-      <c r="F69" s="8" t="n">
+      <c r="F69" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3626,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3636,10 +3698,10 @@
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="B70" s="7" t="n">
+      <c r="B70" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C70" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3647,10 +3709,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E70" s="8" t="n">
+      <c r="E70" s="6" t="n">
         <v>344.1</v>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="6" t="n">
         <v>2.8</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -3675,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3685,10 +3747,10 @@
           <t>2013-04-01</t>
         </is>
       </c>
-      <c r="B71" s="7" t="n">
+      <c r="B71" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C71" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3696,10 +3758,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E71" s="8" t="n">
+      <c r="E71" s="6" t="n">
         <v>358.8</v>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="6" t="n">
         <v>4.3</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -3724,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3734,10 +3796,10 @@
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="B72" s="7" t="n">
+      <c r="B72" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C72" s="7" t="n">
+      <c r="C72" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3745,10 +3807,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E72" s="8" t="n">
+      <c r="E72" s="6" t="n">
         <v>380.7</v>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="6" t="n">
         <v>6.1</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -3773,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3783,10 +3845,10 @@
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="B73" s="7" t="n">
+      <c r="B73" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C73" s="7" t="n">
+      <c r="C73" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3794,10 +3856,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="6" t="n">
         <v>398.6</v>
       </c>
-      <c r="F73" s="8" t="n">
+      <c r="F73" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3822,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3832,10 +3894,10 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="B74" s="7" t="n">
+      <c r="B74" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C74" s="7" t="n">
+      <c r="C74" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3843,10 +3905,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E74" s="8" t="n">
+      <c r="E74" s="6" t="n">
         <v>411.3</v>
       </c>
-      <c r="F74" s="8" t="n">
+      <c r="F74" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -3871,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3881,10 +3943,10 @@
           <t>2013-08-01</t>
         </is>
       </c>
-      <c r="B75" s="7" t="n">
+      <c r="B75" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C75" s="7" t="n">
+      <c r="C75" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3892,10 +3954,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E75" s="8" t="n">
+      <c r="E75" s="6" t="n">
         <v>423.7</v>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F75" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -3920,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3930,10 +3992,10 @@
           <t>2013-09-01</t>
         </is>
       </c>
-      <c r="B76" s="7" t="n">
+      <c r="B76" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C76" s="7" t="n">
+      <c r="C76" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3941,10 +4003,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E76" s="8" t="n">
+      <c r="E76" s="6" t="n">
         <v>442.3</v>
       </c>
-      <c r="F76" s="8" t="n">
+      <c r="F76" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -3969,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -3979,10 +4041,10 @@
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="B77" s="7" t="n">
+      <c r="B77" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C77" s="7" t="n">
+      <c r="C77" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3990,10 +4052,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E77" s="8" t="n">
+      <c r="E77" s="6" t="n">
         <v>464.9</v>
       </c>
-      <c r="F77" s="8" t="n">
+      <c r="F77" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -4018,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4028,10 +4090,10 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="B78" s="7" t="n">
+      <c r="B78" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C78" s="7" t="n">
+      <c r="C78" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4039,10 +4101,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="6" t="n">
         <v>487.3</v>
       </c>
-      <c r="F78" s="8" t="n">
+      <c r="F78" s="6" t="n">
         <v>4.8</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4067,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4077,10 +4139,10 @@
           <t>2013-12-01</t>
         </is>
       </c>
-      <c r="B79" s="7" t="n">
+      <c r="B79" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C79" s="7" t="n">
+      <c r="C79" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4088,10 +4150,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E79" s="8" t="n">
+      <c r="E79" s="6" t="n">
         <v>498.1</v>
       </c>
-      <c r="F79" s="8" t="n">
+      <c r="F79" s="6" t="n">
         <v>2.2</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -4116,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4126,10 +4188,10 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="B80" s="7" t="n">
+      <c r="B80" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C80" s="7" t="n">
+      <c r="C80" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -4137,10 +4199,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E80" s="8" t="n">
+      <c r="E80" s="6" t="n">
         <v>514.7</v>
       </c>
-      <c r="F80" s="8" t="n">
+      <c r="F80" s="6" t="n">
         <v>3.3</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -4165,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4175,10 +4237,10 @@
           <t>2014-02-01</t>
         </is>
       </c>
-      <c r="B81" s="7" t="n">
+      <c r="B81" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C81" s="7" t="n">
+      <c r="C81" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4186,10 +4248,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E81" s="8" t="n">
+      <c r="E81" s="6" t="n">
         <v>526.8</v>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="6" t="n">
         <v>2.4</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4214,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4224,10 +4286,10 @@
           <t>2014-03-01</t>
         </is>
       </c>
-      <c r="B82" s="7" t="n">
+      <c r="B82" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C82" s="7" t="n">
+      <c r="C82" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4235,10 +4297,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E82" s="8" t="n">
+      <c r="E82" s="6" t="n">
         <v>548.3</v>
       </c>
-      <c r="F82" s="8" t="n">
+      <c r="F82" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -4263,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4273,10 +4335,10 @@
           <t>2014-04-01</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C83" s="7" t="n">
+      <c r="C83" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4284,10 +4346,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E83" s="6" t="n">
         <v>579.4</v>
       </c>
-      <c r="F83" s="8" t="n">
+      <c r="F83" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4312,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4322,10 +4384,10 @@
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="B84" s="7" t="n">
+      <c r="B84" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C84" s="7" t="n">
+      <c r="C84" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4333,10 +4395,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E84" s="8" t="n">
+      <c r="E84" s="6" t="n">
         <v>612.6</v>
       </c>
-      <c r="F84" s="8" t="n">
+      <c r="F84" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -4361,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4371,10 +4433,10 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="B85" s="7" t="n">
+      <c r="B85" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C85" s="7" t="n">
+      <c r="C85" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4382,10 +4444,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E85" s="8" t="n">
+      <c r="E85" s="6" t="n">
         <v>639.7</v>
       </c>
-      <c r="F85" s="8" t="n">
+      <c r="F85" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -4410,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4420,10 +4482,10 @@
           <t>2014-07-01</t>
         </is>
       </c>
-      <c r="B86" s="7" t="n">
+      <c r="B86" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C86" s="7" t="n">
+      <c r="C86" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4431,10 +4493,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E86" s="6" t="n">
         <v>666.2</v>
       </c>
-      <c r="F86" s="8" t="n">
+      <c r="F86" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -4459,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4469,10 +4531,10 @@
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="B87" s="7" t="n">
+      <c r="B87" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C87" s="7" t="n">
+      <c r="C87" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -4480,10 +4542,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E87" s="8" t="n">
+      <c r="E87" s="6" t="n">
         <v>692.4</v>
       </c>
-      <c r="F87" s="8" t="n">
+      <c r="F87" s="6" t="n">
         <v>3.9</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4508,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4518,10 +4580,10 @@
           <t>2014-09-01</t>
         </is>
       </c>
-      <c r="B88" s="7" t="n">
+      <c r="B88" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C88" s="7" t="n">
+      <c r="C88" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -4529,10 +4591,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E88" s="8" t="n">
+      <c r="E88" s="6" t="n">
         <v>725.4</v>
       </c>
-      <c r="F88" s="8" t="n">
+      <c r="F88" s="6" t="n">
         <v>4.8</v>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -4557,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4567,10 +4629,10 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="B89" s="7" t="n">
+      <c r="B89" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C89" s="7" t="n">
+      <c r="C89" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -4578,10 +4640,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E89" s="8" t="n">
+      <c r="E89" s="6" t="n">
         <v>761.8</v>
       </c>
-      <c r="F89" s="7" t="n">
+      <c r="F89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4606,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4616,10 +4678,10 @@
           <t>2014-11-01</t>
         </is>
       </c>
-      <c r="B90" s="7" t="n">
+      <c r="B90" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C90" s="7" t="n">
+      <c r="C90" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4627,10 +4689,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E90" s="8" t="n">
+      <c r="E90" s="6" t="n">
         <v>797.3</v>
       </c>
-      <c r="F90" s="8" t="n">
+      <c r="F90" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -4655,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4665,10 +4727,10 @@
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="B91" s="7" t="n">
+      <c r="B91" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4676,10 +4738,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E91" s="8" t="n">
+      <c r="E91" s="6" t="n">
         <v>839.5</v>
       </c>
-      <c r="F91" s="8" t="n">
+      <c r="F91" s="6" t="n">
         <v>5.3</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -4704,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4714,10 +4776,10 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="B92" s="7" t="n">
+      <c r="B92" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -4725,10 +4787,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E92" s="8" t="n">
+      <c r="E92" s="6" t="n">
         <v>904.8</v>
       </c>
-      <c r="F92" s="8" t="n">
+      <c r="F92" s="6" t="n">
         <v>7.8</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -4753,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4763,10 +4825,10 @@
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="B93" s="7" t="n">
+      <c r="B93" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C93" s="7" t="n">
+      <c r="C93" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -4774,10 +4836,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E93" s="8" t="n">
+      <c r="E93" s="6" t="n">
         <v>949.1</v>
       </c>
-      <c r="F93" s="8" t="n">
+      <c r="F93" s="6" t="n">
         <v>4.9</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -4802,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4812,10 +4874,10 @@
           <t>2015-03-01</t>
         </is>
       </c>
-      <c r="B94" s="7" t="n">
+      <c r="B94" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C94" s="7" t="n">
+      <c r="C94" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4823,10 +4885,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E94" s="6" t="n">
         <v>1000.2</v>
       </c>
-      <c r="F94" s="8" t="n">
+      <c r="F94" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -4851,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4861,10 +4923,10 @@
           <t>2015-04-01</t>
         </is>
       </c>
-      <c r="B95" s="7" t="n">
+      <c r="B95" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C95" s="7" t="n">
+      <c r="C95" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4872,10 +4934,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E95" s="8" t="n">
+      <c r="E95" s="6" t="n">
         <v>1063.8</v>
       </c>
-      <c r="F95" s="8" t="n">
+      <c r="F95" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -4900,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4910,10 +4972,10 @@
           <t>2015-05-01</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n">
+      <c r="B96" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C96" s="7" t="n">
+      <c r="C96" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -4921,10 +4983,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E96" s="8" t="n">
+      <c r="E96" s="6" t="n">
         <v>1148.8</v>
       </c>
-      <c r="F96" s="7" t="n">
+      <c r="F96" s="5" t="n">
         <v>8</v>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -4949,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -4959,10 +5021,10 @@
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n">
+      <c r="B97" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C97" s="7" t="n">
+      <c r="C97" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4970,10 +5032,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E97" s="8" t="n">
+      <c r="E97" s="6" t="n">
         <v>1261.6</v>
       </c>
-      <c r="F97" s="8" t="n">
+      <c r="F97" s="6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -4998,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5008,10 +5070,10 @@
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="B98" s="7" t="n">
+      <c r="B98" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C98" s="7" t="n">
+      <c r="C98" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -5019,10 +5081,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E98" s="8" t="n">
+      <c r="E98" s="6" t="n">
         <v>1397.5</v>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -5047,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5057,10 +5119,10 @@
           <t>2015-08-01</t>
         </is>
       </c>
-      <c r="B99" s="7" t="n">
+      <c r="B99" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C99" s="7" t="n">
+      <c r="C99" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -5068,10 +5130,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E99" s="8" t="n">
+      <c r="E99" s="6" t="n">
         <v>1570.8</v>
       </c>
-      <c r="F99" s="8" t="n">
+      <c r="F99" s="6" t="n">
         <v>12.4</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -5096,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5106,10 +5168,10 @@
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="B100" s="7" t="n">
+      <c r="B100" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C100" s="7" t="n">
+      <c r="C100" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -5117,10 +5179,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E100" s="8" t="n">
+      <c r="E100" s="6" t="n">
         <v>1752.1</v>
       </c>
-      <c r="F100" s="8" t="n">
+      <c r="F100" s="6" t="n">
         <v>11.5</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -5145,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5155,10 +5217,10 @@
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="B101" s="7" t="n">
+      <c r="B101" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C101" s="7" t="n">
+      <c r="C101" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -5166,10 +5228,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E101" s="8" t="n">
+      <c r="E101" s="6" t="n">
         <v>1951.3</v>
       </c>
-      <c r="F101" s="8" t="n">
+      <c r="F101" s="6" t="n">
         <v>11.4</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -5194,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5204,10 +5266,10 @@
           <t>2015-11-01</t>
         </is>
       </c>
-      <c r="B102" s="7" t="n">
+      <c r="B102" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C102" s="7" t="n">
+      <c r="C102" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -5215,10 +5277,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E102" s="8" t="n">
+      <c r="E102" s="6" t="n">
         <v>2168.5</v>
       </c>
-      <c r="F102" s="8" t="n">
+      <c r="F102" s="6" t="n">
         <v>11.1</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -5243,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5253,10 +5315,10 @@
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="B103" s="7" t="n">
+      <c r="B103" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C103" s="7" t="n">
+      <c r="C103" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -5264,10 +5326,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E103" s="8" t="n">
+      <c r="E103" s="6" t="n">
         <v>2357.9</v>
       </c>
-      <c r="F103" s="8" t="n">
+      <c r="F103" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -5292,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5302,10 +5364,10 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="B104" s="7" t="n">
+      <c r="B104" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C104" s="7" t="n">
+      <c r="C104" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -5313,10 +5375,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E104" s="8" t="n">
+      <c r="E104" s="6" t="n">
         <v>2576.5</v>
       </c>
-      <c r="F104" s="8" t="n">
+      <c r="F104" s="6" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -5341,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5351,10 +5413,10 @@
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="B105" s="7" t="n">
+      <c r="B105" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C105" s="7" t="n">
+      <c r="C105" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -5362,10 +5424,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E105" s="8" t="n">
+      <c r="E105" s="6" t="n">
         <v>2801.1</v>
       </c>
-      <c r="F105" s="8" t="n">
+      <c r="F105" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -5390,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5400,10 +5462,10 @@
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="B106" s="7" t="n">
+      <c r="B106" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C106" s="7" t="n">
+      <c r="C106" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -5411,10 +5473,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E106" s="8" t="n">
+      <c r="E106" s="6" t="n">
         <v>3096.2</v>
       </c>
-      <c r="F106" s="8" t="n">
+      <c r="F106" s="6" t="n">
         <v>10.5</v>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -5439,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5449,10 +5511,10 @@
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="B107" s="7" t="n">
+      <c r="B107" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C107" s="7" t="n">
+      <c r="C107" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -5460,10 +5522,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E107" s="8" t="n">
+      <c r="E107" s="6" t="n">
         <v>3541.6</v>
       </c>
-      <c r="F107" s="8" t="n">
+      <c r="F107" s="6" t="n">
         <v>14.4</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -5488,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5498,10 +5560,10 @@
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="B108" s="7" t="n">
+      <c r="B108" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C108" s="7" t="n">
+      <c r="C108" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -5509,10 +5571,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E108" s="8" t="n">
+      <c r="E108" s="6" t="n">
         <v>4195.9</v>
       </c>
-      <c r="F108" s="8" t="n">
+      <c r="F108" s="6" t="n">
         <v>18.5</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -5537,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5547,10 +5609,10 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="B109" s="7" t="n">
+      <c r="B109" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C109" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -5558,10 +5620,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E109" s="8" t="n">
+      <c r="E109" s="6" t="n">
         <v>5001.5</v>
       </c>
-      <c r="F109" s="8" t="n">
+      <c r="F109" s="6" t="n">
         <v>19.2</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -5586,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5596,10 +5658,10 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="B110" s="7" t="n">
+      <c r="B110" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C110" s="7" t="n">
+      <c r="C110" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -5607,10 +5669,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E110" s="8" t="n">
+      <c r="E110" s="6" t="n">
         <v>5437.1</v>
       </c>
-      <c r="F110" s="8" t="n">
+      <c r="F110" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -5635,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5645,10 +5707,10 @@
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="B111" s="7" t="n">
+      <c r="B111" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C111" s="7" t="n">
+      <c r="C111" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -5656,10 +5718,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E111" s="8" t="n">
+      <c r="E111" s="6" t="n">
         <v>5825.7</v>
       </c>
-      <c r="F111" s="8" t="n">
+      <c r="F111" s="6" t="n">
         <v>7.1</v>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -5684,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5694,10 +5756,10 @@
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="B112" s="7" t="n">
+      <c r="B112" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C112" s="7" t="n">
+      <c r="C112" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -5705,10 +5767,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E112" s="8" t="n">
+      <c r="E112" s="6" t="n">
         <v>6364.4</v>
       </c>
-      <c r="F112" s="8" t="n">
+      <c r="F112" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -5733,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5743,10 +5805,10 @@
           <t>2016-10-01</t>
         </is>
       </c>
-      <c r="B113" s="7" t="n">
+      <c r="B113" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C113" s="7" t="n">
+      <c r="C113" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -5754,10 +5816,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E113" s="8" t="n">
+      <c r="E113" s="6" t="n">
         <v>6873.9</v>
       </c>
-      <c r="F113" s="7" t="n">
+      <c r="F113" s="5" t="n">
         <v>8</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -5782,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5792,10 +5854,10 @@
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="B114" s="7" t="n">
+      <c r="B114" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C114" s="7" t="n">
+      <c r="C114" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -5803,10 +5865,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E114" s="8" t="n">
+      <c r="E114" s="6" t="n">
         <v>7668.9</v>
       </c>
-      <c r="F114" s="8" t="n">
+      <c r="F114" s="6" t="n">
         <v>11.6</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -5831,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5903,10 @@
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="B115" s="7" t="n">
+      <c r="B115" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C115" s="7" t="n">
+      <c r="C115" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -5852,10 +5914,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E115" s="8" t="n">
+      <c r="E115" s="6" t="n">
         <v>8826.9</v>
       </c>
-      <c r="F115" s="8" t="n">
+      <c r="F115" s="6" t="n">
         <v>15.1</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -5880,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5890,10 +5952,10 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="B116" s="7" t="n">
+      <c r="B116" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C116" s="7" t="n">
+      <c r="C116" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -5901,10 +5963,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E116" s="8" t="n">
+      <c r="E116" s="6" t="n">
         <v>10378.1</v>
       </c>
-      <c r="F116" s="8" t="n">
+      <c r="F116" s="6" t="n">
         <v>17.6</v>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -5929,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5939,10 +6001,10 @@
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="B117" s="7" t="n">
+      <c r="B117" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C117" s="7" t="n">
+      <c r="C117" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -5950,10 +6012,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E117" s="8" t="n">
+      <c r="E117" s="6" t="n">
         <v>11697.2</v>
       </c>
-      <c r="F117" s="8" t="n">
+      <c r="F117" s="6" t="n">
         <v>12.7</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -5978,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -5988,10 +6050,10 @@
           <t>2017-03-01</t>
         </is>
       </c>
-      <c r="B118" s="7" t="n">
+      <c r="B118" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C118" s="7" t="n">
+      <c r="C118" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -5999,10 +6061,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E118" s="8" t="n">
+      <c r="E118" s="6" t="n">
         <v>12910.1</v>
       </c>
-      <c r="F118" s="8" t="n">
+      <c r="F118" s="6" t="n">
         <v>10.4</v>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6027,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6037,10 +6099,10 @@
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="B119" s="7" t="n">
+      <c r="B119" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C119" s="7" t="n">
+      <c r="C119" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -6048,10 +6110,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E119" s="8" t="n">
+      <c r="E119" s="6" t="n">
         <v>13975.9</v>
       </c>
-      <c r="F119" s="8" t="n">
+      <c r="F119" s="6" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -6076,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6086,10 +6148,10 @@
           <t>2017-05-01</t>
         </is>
       </c>
-      <c r="B120" s="7" t="n">
+      <c r="B120" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C120" s="7" t="n">
+      <c r="C120" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -6097,10 +6159,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E120" s="8" t="n">
+      <c r="E120" s="6" t="n">
         <v>15610.4</v>
       </c>
-      <c r="F120" s="8" t="n">
+      <c r="F120" s="6" t="n">
         <v>11.7</v>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -6125,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6135,10 +6197,10 @@
           <t>2017-06-01</t>
         </is>
       </c>
-      <c r="B121" s="7" t="n">
+      <c r="B121" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C121" s="7" t="n">
+      <c r="C121" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -6146,10 +6208,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E121" s="8" t="n">
+      <c r="E121" s="6" t="n">
         <v>17537.8</v>
       </c>
-      <c r="F121" s="8" t="n">
+      <c r="F121" s="6" t="n">
         <v>12.3</v>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -6174,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6184,10 +6246,10 @@
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="B122" s="7" t="n">
+      <c r="B122" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C122" s="7" t="n">
+      <c r="C122" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -6195,10 +6257,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E122" s="8" t="n">
+      <c r="E122" s="6" t="n">
         <v>19938.2</v>
       </c>
-      <c r="F122" s="8" t="n">
+      <c r="F122" s="6" t="n">
         <v>13.7</v>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -6223,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6233,10 +6295,10 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="B123" s="7" t="n">
+      <c r="B123" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C123" s="7" t="n">
+      <c r="C123" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -6244,10 +6306,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E123" s="8" t="n">
+      <c r="E123" s="6" t="n">
         <v>23736.3</v>
       </c>
-      <c r="F123" s="7" t="n">
+      <c r="F123" s="5" t="n">
         <v>19</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -6272,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6282,10 +6344,10 @@
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="B124" s="7" t="n">
+      <c r="B124" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C124" s="7" t="n">
+      <c r="C124" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -6293,10 +6355,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E124" s="8" t="n">
+      <c r="E124" s="6" t="n">
         <v>29921.9</v>
       </c>
-      <c r="F124" s="8" t="n">
+      <c r="F124" s="6" t="n">
         <v>26.1</v>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -6321,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6331,10 +6393,10 @@
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="B125" s="7" t="n">
+      <c r="B125" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C125" s="7" t="n">
+      <c r="C125" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -6342,10 +6404,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E125" s="8" t="n">
+      <c r="E125" s="6" t="n">
         <v>39473.9</v>
       </c>
-      <c r="F125" s="8" t="n">
+      <c r="F125" s="6" t="n">
         <v>31.9</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -6370,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6380,10 +6442,10 @@
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="B126" s="7" t="n">
+      <c r="B126" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C126" s="7" t="n">
+      <c r="C126" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -6391,10 +6453,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n">
+      <c r="E126" s="5" t="n">
         <v>54611</v>
       </c>
-      <c r="F126" s="8" t="n">
+      <c r="F126" s="6" t="n">
         <v>38.3</v>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -6419,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6429,10 +6491,10 @@
           <t>2017-12-01</t>
         </is>
       </c>
-      <c r="B127" s="7" t="n">
+      <c r="B127" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C127" s="7" t="n">
+      <c r="C127" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -6440,10 +6502,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E127" s="8" t="n">
+      <c r="E127" s="6" t="n">
         <v>84970.3</v>
       </c>
-      <c r="F127" s="8" t="n">
+      <c r="F127" s="6" t="n">
         <v>55.6</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -6468,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6478,10 +6540,10 @@
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="B128" s="7" t="n">
+      <c r="B128" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C128" s="7" t="n">
+      <c r="C128" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -6489,10 +6551,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E128" s="8" t="n">
+      <c r="E128" s="6" t="n">
         <v>141060.9</v>
       </c>
-      <c r="F128" s="7" t="n">
+      <c r="F128" s="5" t="n">
         <v>66</v>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -6517,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6527,10 +6589,10 @@
           <t>2018-02-01</t>
         </is>
       </c>
-      <c r="B129" s="7" t="n">
+      <c r="B129" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C129" s="7" t="n">
+      <c r="C129" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -6538,10 +6600,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E129" s="8" t="n">
+      <c r="E129" s="6" t="n">
         <v>204074.2</v>
       </c>
-      <c r="F129" s="8" t="n">
+      <c r="F129" s="6" t="n">
         <v>44.7</v>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -6566,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6576,10 +6638,10 @@
           <t>2018-03-01</t>
         </is>
       </c>
-      <c r="B130" s="7" t="n">
+      <c r="B130" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C130" s="7" t="n">
+      <c r="C130" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -6587,10 +6649,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E130" s="8" t="n">
+      <c r="E130" s="6" t="n">
         <v>287622.2</v>
       </c>
-      <c r="F130" s="8" t="n">
+      <c r="F130" s="6" t="n">
         <v>40.9</v>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -6615,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6625,10 +6687,10 @@
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="B131" s="7" t="n">
+      <c r="B131" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C131" s="7" t="n">
+      <c r="C131" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -6636,10 +6698,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E131" s="7" t="n">
+      <c r="E131" s="5" t="n">
         <v>448124</v>
       </c>
-      <c r="F131" s="8" t="n">
+      <c r="F131" s="6" t="n">
         <v>55.8</v>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -6664,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6674,10 +6736,10 @@
           <t>2018-05-01</t>
         </is>
       </c>
-      <c r="B132" s="7" t="n">
+      <c r="B132" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C132" s="7" t="n">
+      <c r="C132" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -6685,10 +6747,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E132" s="7" t="n">
+      <c r="E132" s="5" t="n">
         <v>942481</v>
       </c>
-      <c r="F132" s="8" t="n">
+      <c r="F132" s="6" t="n">
         <v>110.3</v>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -6713,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6723,10 +6785,10 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="B133" s="7" t="n">
+      <c r="B133" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C133" s="7" t="n">
+      <c r="C133" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -6734,10 +6796,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E133" s="8" t="n">
+      <c r="E133" s="6" t="n">
         <v>1853869.6</v>
       </c>
-      <c r="F133" s="8" t="n">
+      <c r="F133" s="6" t="n">
         <v>96.7</v>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -6762,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6772,10 +6834,10 @@
           <t>2018-07-01</t>
         </is>
       </c>
-      <c r="B134" s="7" t="n">
+      <c r="B134" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C134" s="7" t="n">
+      <c r="C134" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -6783,10 +6845,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E134" s="8" t="n">
+      <c r="E134" s="6" t="n">
         <v>3362789.7</v>
       </c>
-      <c r="F134" s="8" t="n">
+      <c r="F134" s="6" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -6811,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6821,10 +6883,10 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="B135" s="7" t="n">
+      <c r="B135" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C135" s="7" t="n">
+      <c r="C135" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -6832,10 +6894,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E135" s="8" t="n">
+      <c r="E135" s="6" t="n">
         <v>5919047.9</v>
       </c>
-      <c r="F135" s="7" t="n">
+      <c r="F135" s="5" t="n">
         <v>76</v>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -6860,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6870,10 +6932,10 @@
           <t>2018-09-01</t>
         </is>
       </c>
-      <c r="B136" s="7" t="n">
+      <c r="B136" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C136" s="7" t="n">
+      <c r="C136" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -6881,10 +6943,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E136" s="8" t="n">
+      <c r="E136" s="6" t="n">
         <v>13479980.5</v>
       </c>
-      <c r="F136" s="8" t="n">
+      <c r="F136" s="6" t="n">
         <v>127.7</v>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -6909,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6919,10 +6981,10 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="B137" s="7" t="n">
+      <c r="B137" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C137" s="7" t="n">
+      <c r="C137" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -6930,10 +6992,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E137" s="8" t="n">
+      <c r="E137" s="6" t="n">
         <v>25355573.7</v>
       </c>
-      <c r="F137" s="8" t="n">
+      <c r="F137" s="6" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -6958,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -6968,10 +7030,10 @@
           <t>2018-11-01</t>
         </is>
       </c>
-      <c r="B138" s="7" t="n">
+      <c r="B138" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C138" s="7" t="n">
+      <c r="C138" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -6979,10 +7041,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E138" s="8" t="n">
+      <c r="E138" s="6" t="n">
         <v>56589583.5</v>
       </c>
-      <c r="F138" s="8" t="n">
+      <c r="F138" s="6" t="n">
         <v>123.2</v>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -7007,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7017,10 +7079,10 @@
           <t>2018-12-01</t>
         </is>
       </c>
-      <c r="B139" s="7" t="n">
+      <c r="B139" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C139" s="7" t="n">
+      <c r="C139" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -7028,10 +7090,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E139" s="8" t="n">
+      <c r="E139" s="6" t="n">
         <v>110597550.2</v>
       </c>
-      <c r="F139" s="8" t="n">
+      <c r="F139" s="6" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -7056,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7066,10 +7128,10 @@
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="B140" s="7" t="n">
+      <c r="B140" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C140" s="7" t="n">
+      <c r="C140" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -7077,10 +7139,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E140" s="8" t="n">
+      <c r="E140" s="6" t="n">
         <v>328067725.1</v>
       </c>
-      <c r="F140" s="8" t="n">
+      <c r="F140" s="6" t="n">
         <v>196.6</v>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -7105,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7115,10 +7177,10 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="B141" s="7" t="n">
+      <c r="B141" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C141" s="7" t="n">
+      <c r="C141" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -7126,10 +7188,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E141" s="8" t="n">
+      <c r="E141" s="6" t="n">
         <v>703259098.2</v>
       </c>
-      <c r="F141" s="8" t="n">
+      <c r="F141" s="6" t="n">
         <v>114.4</v>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -7154,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7164,10 +7226,10 @@
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="B142" s="7" t="n">
+      <c r="B142" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C142" s="7" t="n">
+      <c r="C142" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -7175,10 +7237,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E142" s="8" t="n">
+      <c r="E142" s="6" t="n">
         <v>948197209.5</v>
       </c>
-      <c r="F142" s="8" t="n">
+      <c r="F142" s="6" t="n">
         <v>34.8</v>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -7203,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7213,10 +7275,10 @@
           <t>2019-04-01</t>
         </is>
       </c>
-      <c r="B143" s="7" t="n">
+      <c r="B143" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C143" s="7" t="n">
+      <c r="C143" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -7224,10 +7286,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E143" s="8" t="n">
+      <c r="E143" s="6" t="n">
         <v>1268517190.9</v>
       </c>
-      <c r="F143" s="8" t="n">
+      <c r="F143" s="6" t="n">
         <v>33.8</v>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -7252,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7262,10 +7324,10 @@
           <t>2019-05-01</t>
         </is>
       </c>
-      <c r="B144" s="7" t="n">
+      <c r="B144" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C144" s="7" t="n">
+      <c r="C144" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -7273,10 +7335,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E144" s="8" t="n">
+      <c r="E144" s="6" t="n">
         <v>1769365833.3</v>
       </c>
-      <c r="F144" s="8" t="n">
+      <c r="F144" s="6" t="n">
         <v>39.5</v>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -7301,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7311,10 +7373,10 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="B145" s="7" t="n">
+      <c r="B145" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C145" s="7" t="n">
+      <c r="C145" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -7322,10 +7384,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E145" s="6" t="n">
         <v>2160431069.8</v>
       </c>
-      <c r="F145" s="8" t="n">
+      <c r="F145" s="6" t="n">
         <v>22.1</v>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -7350,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7360,10 +7422,10 @@
           <t>2019-07-01</t>
         </is>
       </c>
-      <c r="B146" s="7" t="n">
+      <c r="B146" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C146" s="7" t="n">
+      <c r="C146" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -7371,10 +7433,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E146" s="8" t="n">
+      <c r="E146" s="6" t="n">
         <v>2579165819.7</v>
       </c>
-      <c r="F146" s="8" t="n">
+      <c r="F146" s="6" t="n">
         <v>19.4</v>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -7399,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7409,10 +7471,10 @@
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="B147" s="7" t="n">
+      <c r="B147" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C147" s="7" t="n">
+      <c r="C147" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -7420,10 +7482,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E147" s="8" t="n">
+      <c r="E147" s="6" t="n">
         <v>3472176193.2</v>
       </c>
-      <c r="F147" s="8" t="n">
+      <c r="F147" s="6" t="n">
         <v>34.6</v>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -7448,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7458,10 +7520,10 @@
           <t>2019-09-01</t>
         </is>
       </c>
-      <c r="B148" s="7" t="n">
+      <c r="B148" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C148" s="7" t="n">
+      <c r="C148" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -7469,10 +7531,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E148" s="8" t="n">
+      <c r="E148" s="6" t="n">
         <v>5286006314.7</v>
       </c>
-      <c r="F148" s="8" t="n">
+      <c r="F148" s="6" t="n">
         <v>52.2</v>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -7497,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7507,10 +7569,10 @@
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="B149" s="7" t="n">
+      <c r="B149" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C149" s="7" t="n">
+      <c r="C149" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -7518,10 +7580,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E149" s="8" t="n">
+      <c r="E149" s="6" t="n">
         <v>6478423619.2</v>
       </c>
-      <c r="F149" s="8" t="n">
+      <c r="F149" s="6" t="n">
         <v>22.6</v>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -7546,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7556,10 +7618,10 @@
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="B150" s="7" t="n">
+      <c r="B150" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C150" s="7" t="n">
+      <c r="C150" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -7567,10 +7629,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E150" s="8" t="n">
+      <c r="E150" s="6" t="n">
         <v>8144026331.7</v>
       </c>
-      <c r="F150" s="8" t="n">
+      <c r="F150" s="6" t="n">
         <v>25.7</v>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -7595,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7605,10 +7667,10 @@
           <t>2019-12-01</t>
         </is>
       </c>
-      <c r="B151" s="7" t="n">
+      <c r="B151" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C151" s="7" t="n">
+      <c r="C151" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -7616,10 +7678,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E151" s="8" t="n">
+      <c r="E151" s="6" t="n">
         <v>10711919274.4</v>
       </c>
-      <c r="F151" s="8" t="n">
+      <c r="F151" s="6" t="n">
         <v>31.5</v>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -7644,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7654,10 +7716,10 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="B152" s="7" t="n">
+      <c r="B152" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C152" s="7" t="n">
+      <c r="C152" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -7665,10 +7727,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E152" s="8" t="n">
+      <c r="E152" s="6" t="n">
         <v>17377625281.2</v>
       </c>
-      <c r="F152" s="8" t="n">
+      <c r="F152" s="6" t="n">
         <v>62.2</v>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -7693,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7703,10 +7765,10 @@
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="B153" s="7" t="n">
+      <c r="B153" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C153" s="7" t="n">
+      <c r="C153" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -7714,10 +7776,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E153" s="8" t="n">
+      <c r="E153" s="6" t="n">
         <v>21174462628.9</v>
       </c>
-      <c r="F153" s="8" t="n">
+      <c r="F153" s="6" t="n">
         <v>21.8</v>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -7742,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7752,10 +7814,10 @@
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="B154" s="7" t="n">
+      <c r="B154" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C154" s="7" t="n">
+      <c r="C154" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -7763,10 +7825,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E154" s="8" t="n">
+      <c r="E154" s="6" t="n">
         <v>23995112795.7</v>
       </c>
-      <c r="F154" s="8" t="n">
+      <c r="F154" s="6" t="n">
         <v>13.3</v>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -7791,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7801,10 +7863,10 @@
           <t>2020-04-01</t>
         </is>
       </c>
-      <c r="B155" s="7" t="n">
+      <c r="B155" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C155" s="7" t="n">
+      <c r="C155" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -7812,10 +7874,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E155" s="8" t="n">
+      <c r="E155" s="6" t="n">
         <v>30594008765.7</v>
       </c>
-      <c r="F155" s="8" t="n">
+      <c r="F155" s="6" t="n">
         <v>27.5</v>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -7840,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7850,10 +7912,10 @@
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="B156" s="7" t="n">
+      <c r="B156" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C156" s="7" t="n">
+      <c r="C156" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -7861,10 +7923,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E156" s="8" t="n">
+      <c r="E156" s="6" t="n">
         <v>42404519909.6</v>
       </c>
-      <c r="F156" s="8" t="n">
+      <c r="F156" s="6" t="n">
         <v>38.6</v>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -7889,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7899,10 +7961,10 @@
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="B157" s="7" t="n">
+      <c r="B157" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C157" s="7" t="n">
+      <c r="C157" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -7910,10 +7972,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E157" s="8" t="n">
+      <c r="E157" s="6" t="n">
         <v>53033212824.9</v>
       </c>
-      <c r="F157" s="8" t="n">
+      <c r="F157" s="6" t="n">
         <v>25.1</v>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -7938,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7948,10 +8010,10 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="B158" s="7" t="n">
+      <c r="B158" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C158" s="7" t="n">
+      <c r="C158" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -7959,10 +8021,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E158" s="8" t="n">
+      <c r="E158" s="6" t="n">
         <v>63408630581.9</v>
       </c>
-      <c r="F158" s="8" t="n">
+      <c r="F158" s="6" t="n">
         <v>19.6</v>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -7987,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -7997,10 +8059,10 @@
           <t>2020-08-01</t>
         </is>
       </c>
-      <c r="B159" s="7" t="n">
+      <c r="B159" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C159" s="7" t="n">
+      <c r="C159" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -8008,10 +8070,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E159" s="8" t="n">
+      <c r="E159" s="6" t="n">
         <v>79061685127.39999</v>
       </c>
-      <c r="F159" s="8" t="n">
+      <c r="F159" s="6" t="n">
         <v>24.7</v>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -8036,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8046,10 +8108,10 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="B160" s="7" t="n">
+      <c r="B160" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C160" s="7" t="n">
+      <c r="C160" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -8057,10 +8119,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E160" s="8" t="n">
+      <c r="E160" s="6" t="n">
         <v>101126220212.8</v>
       </c>
-      <c r="F160" s="8" t="n">
+      <c r="F160" s="6" t="n">
         <v>27.9</v>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -8085,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8095,10 +8157,10 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="B161" s="7" t="n">
+      <c r="B161" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C161" s="7" t="n">
+      <c r="C161" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -8106,10 +8168,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E161" s="8" t="n">
+      <c r="E161" s="6" t="n">
         <v>131945447084.8</v>
       </c>
-      <c r="F161" s="8" t="n">
+      <c r="F161" s="6" t="n">
         <v>30.5</v>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -8134,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8144,10 +8206,10 @@
           <t>2020-11-01</t>
         </is>
       </c>
-      <c r="B162" s="7" t="n">
+      <c r="B162" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C162" s="7" t="n">
+      <c r="C162" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -8155,10 +8217,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E162" s="8" t="n">
+      <c r="E162" s="6" t="n">
         <v>184682722830.1</v>
       </c>
-      <c r="F162" s="7" t="n">
+      <c r="F162" s="5" t="n">
         <v>40</v>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -8183,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8193,10 +8255,10 @@
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="B163" s="7" t="n">
+      <c r="B163" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C163" s="7" t="n">
+      <c r="C163" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -8204,10 +8266,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E163" s="7" t="n">
+      <c r="E163" s="5" t="n">
         <v>327767509170</v>
       </c>
-      <c r="F163" s="8" t="n">
+      <c r="F163" s="6" t="n">
         <v>77.5</v>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -8232,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8242,10 +8304,10 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="B164" s="7" t="n">
+      <c r="B164" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C164" s="7" t="n">
+      <c r="C164" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -8253,10 +8315,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E164" s="8" t="n">
+      <c r="E164" s="6" t="n">
         <v>480553055894.4</v>
       </c>
-      <c r="F164" s="8" t="n">
+      <c r="F164" s="6" t="n">
         <v>46.6</v>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -8281,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8291,10 +8353,10 @@
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="B165" s="7" t="n">
+      <c r="B165" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C165" s="7" t="n">
+      <c r="C165" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -8302,10 +8364,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E165" s="8" t="n">
+      <c r="E165" s="6" t="n">
         <v>643008821970.1</v>
       </c>
-      <c r="F165" s="8" t="n">
+      <c r="F165" s="6" t="n">
         <v>33.8</v>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -8330,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8340,10 +8402,10 @@
           <t>2021-03-01</t>
         </is>
       </c>
-      <c r="B166" s="7" t="n">
+      <c r="B166" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C166" s="7" t="n">
+      <c r="C166" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -8351,10 +8413,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E166" s="8" t="n">
+      <c r="E166" s="6" t="n">
         <v>746784015747.9</v>
       </c>
-      <c r="F166" s="8" t="n">
+      <c r="F166" s="6" t="n">
         <v>16.1</v>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -8379,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8389,10 +8451,10 @@
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="B167" s="7" t="n">
+      <c r="B167" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C167" s="7" t="n">
+      <c r="C167" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -8400,10 +8462,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E167" s="8" t="n">
+      <c r="E167" s="6" t="n">
         <v>930306187617.9</v>
       </c>
-      <c r="F167" s="8" t="n">
+      <c r="F167" s="6" t="n">
         <v>24.6</v>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -8428,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8438,10 +8500,10 @@
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="B168" s="7" t="n">
+      <c r="B168" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C168" s="7" t="n">
+      <c r="C168" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -8449,10 +8511,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E168" s="8" t="n">
+      <c r="E168" s="6" t="n">
         <v>1195582997017.2</v>
       </c>
-      <c r="F168" s="8" t="n">
+      <c r="F168" s="6" t="n">
         <v>28.5</v>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -8477,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8487,10 +8549,10 @@
           <t>2021-06-01</t>
         </is>
       </c>
-      <c r="B169" s="7" t="n">
+      <c r="B169" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C169" s="7" t="n">
+      <c r="C169" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -8498,10 +8560,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E169" s="8" t="n">
+      <c r="E169" s="6" t="n">
         <v>1383038455119.5</v>
       </c>
-      <c r="F169" s="8" t="n">
+      <c r="F169" s="6" t="n">
         <v>15.7</v>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -8526,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8536,10 +8598,10 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="B170" s="7" t="n">
+      <c r="B170" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C170" s="7" t="n">
+      <c r="C170" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -8547,10 +8609,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E170" s="8" t="n">
+      <c r="E170" s="6" t="n">
         <v>1613383509819.7</v>
       </c>
-      <c r="F170" s="8" t="n">
+      <c r="F170" s="6" t="n">
         <v>16.7</v>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -8575,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8585,10 +8647,10 @@
           <t>2021-08-01</t>
         </is>
       </c>
-      <c r="B171" s="7" t="n">
+      <c r="B171" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C171" s="7" t="n">
+      <c r="C171" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -8596,10 +8658,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E171" s="8" t="n">
+      <c r="E171" s="6" t="n">
         <v>1932171957524.9</v>
       </c>
-      <c r="F171" s="8" t="n">
+      <c r="F171" s="6" t="n">
         <v>19.8</v>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -8624,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8634,10 +8696,10 @@
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="B172" s="7" t="n">
+      <c r="B172" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C172" s="7" t="n">
+      <c r="C172" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -8645,10 +8707,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E172" s="8" t="n">
+      <c r="E172" s="6" t="n">
         <v>2069027697276.4</v>
       </c>
-      <c r="F172" s="8" t="n">
+      <c r="F172" s="6" t="n">
         <v>7.1</v>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -8673,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8683,10 +8745,10 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="B173" s="7" t="n">
+      <c r="B173" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C173" s="7" t="n">
+      <c r="C173" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -8694,10 +8756,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E173" s="8" t="n">
+      <c r="E173" s="6" t="n">
         <v>2210425050108.3</v>
       </c>
-      <c r="F173" s="8" t="n">
+      <c r="F173" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -8722,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8732,10 +8794,10 @@
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="B174" s="7" t="n">
+      <c r="B174" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C174" s="7" t="n">
+      <c r="C174" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -8743,10 +8805,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E174" s="8" t="n">
+      <c r="E174" s="6" t="n">
         <v>2396255484070.9</v>
       </c>
-      <c r="F174" s="8" t="n">
+      <c r="F174" s="6" t="n">
         <v>8.4</v>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -8771,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8781,10 +8843,10 @@
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="B175" s="7" t="n">
+      <c r="B175" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C175" s="7" t="n">
+      <c r="C175" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -8792,10 +8854,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E175" s="7" t="n">
+      <c r="E175" s="5" t="n">
         <v>2577508248886</v>
       </c>
-      <c r="F175" s="8" t="n">
+      <c r="F175" s="6" t="n">
         <v>7.6</v>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -8820,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8830,10 +8892,10 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="B176" s="7" t="n">
+      <c r="B176" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C176" s="7" t="n">
+      <c r="C176" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -8841,10 +8903,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E176" s="7" t="n">
+      <c r="E176" s="5" t="n">
         <v>2750974554036</v>
       </c>
-      <c r="F176" s="8" t="n">
+      <c r="F176" s="6" t="n">
         <v>6.7</v>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -8869,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8879,10 +8941,10 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="B177" s="7" t="n">
+      <c r="B177" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C177" s="7" t="n">
+      <c r="C177" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -8890,10 +8952,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E177" s="8" t="n">
+      <c r="E177" s="6" t="n">
         <v>2832100793634.5</v>
       </c>
-      <c r="F177" s="8" t="n">
+      <c r="F177" s="6" t="n">
         <v>2.9</v>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -8918,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8928,10 +8990,10 @@
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="B178" s="7" t="n">
+      <c r="B178" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C178" s="7" t="n">
+      <c r="C178" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -8939,10 +9001,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E178" s="8" t="n">
+      <c r="E178" s="6" t="n">
         <v>2870702327451.8</v>
       </c>
-      <c r="F178" s="8" t="n">
+      <c r="F178" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -8967,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -8977,10 +9039,10 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="B179" s="7" t="n">
+      <c r="B179" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C179" s="7" t="n">
+      <c r="C179" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -8988,10 +9050,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E179" s="8" t="n">
+      <c r="E179" s="6" t="n">
         <v>2997960561627.7</v>
       </c>
-      <c r="F179" s="8" t="n">
+      <c r="F179" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -9016,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9026,10 +9088,10 @@
           <t>2022-05-01</t>
         </is>
       </c>
-      <c r="B180" s="7" t="n">
+      <c r="B180" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C180" s="7" t="n">
+      <c r="C180" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -9037,10 +9099,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E180" s="8" t="n">
+      <c r="E180" s="6" t="n">
         <v>3194057161963.8</v>
       </c>
-      <c r="F180" s="8" t="n">
+      <c r="F180" s="6" t="n">
         <v>6.5</v>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -9065,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9075,10 +9137,10 @@
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="B181" s="7" t="n">
+      <c r="B181" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C181" s="7" t="n">
+      <c r="C181" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -9086,10 +9148,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E181" s="8" t="n">
+      <c r="E181" s="6" t="n">
         <v>3557760912588.8</v>
       </c>
-      <c r="F181" s="8" t="n">
+      <c r="F181" s="6" t="n">
         <v>11.4</v>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -9114,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9124,10 +9186,10 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="B182" s="7" t="n">
+      <c r="B182" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C182" s="7" t="n">
+      <c r="C182" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -9135,10 +9197,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E182" s="8" t="n">
+      <c r="E182" s="6" t="n">
         <v>3825157521197.5</v>
       </c>
-      <c r="F182" s="8" t="n">
+      <c r="F182" s="6" t="n">
         <v>7.5</v>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -9163,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9173,10 +9235,10 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="B183" s="7" t="n">
+      <c r="B183" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C183" s="7" t="n">
+      <c r="C183" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -9184,10 +9246,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E183" s="8" t="n">
+      <c r="E183" s="6" t="n">
         <v>4137433044225.2</v>
       </c>
-      <c r="F183" s="8" t="n">
+      <c r="F183" s="6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -9212,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9222,10 +9284,10 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="B184" s="7" t="n">
+      <c r="B184" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C184" s="7" t="n">
+      <c r="C184" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -9233,10 +9295,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E184" s="8" t="n">
+      <c r="E184" s="6" t="n">
         <v>5326371620985.8</v>
       </c>
-      <c r="F184" s="8" t="n">
+      <c r="F184" s="6" t="n">
         <v>28.7</v>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -9261,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9271,10 +9333,10 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="B185" s="7" t="n">
+      <c r="B185" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C185" s="7" t="n">
+      <c r="C185" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -9282,10 +9344,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E185" s="8" t="n">
+      <c r="E185" s="6" t="n">
         <v>5654207045137.4</v>
       </c>
-      <c r="F185" s="8" t="n">
+      <c r="F185" s="6" t="n">
         <v>6.2</v>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -9310,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9320,10 +9382,10 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="B186" s="7" t="n">
+      <c r="B186" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C186" s="7" t="n">
+      <c r="C186" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -9331,10 +9393,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E186" s="8" t="n">
+      <c r="E186" s="6" t="n">
         <v>6364445508067.7</v>
       </c>
-      <c r="F186" s="8" t="n">
+      <c r="F186" s="6" t="n">
         <v>12.6</v>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -9359,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9369,10 +9431,10 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="B187" s="7" t="n">
+      <c r="B187" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C187" s="7" t="n">
+      <c r="C187" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -9380,10 +9442,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E187" s="8" t="n">
+      <c r="E187" s="6" t="n">
         <v>8610897384090.4</v>
       </c>
-      <c r="F187" s="8" t="n">
+      <c r="F187" s="6" t="n">
         <v>35.3</v>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -9408,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9418,10 +9480,10 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="B188" s="7" t="n">
+      <c r="B188" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C188" s="7" t="n">
+      <c r="C188" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -9429,10 +9491,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E188" s="8" t="n">
+      <c r="E188" s="6" t="n">
         <v>12239280550707.2</v>
       </c>
-      <c r="F188" s="8" t="n">
+      <c r="F188" s="6" t="n">
         <v>42.1</v>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -9457,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9467,10 +9529,10 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="B189" s="7" t="n">
+      <c r="B189" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C189" s="7" t="n">
+      <c r="C189" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -9478,10 +9540,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E189" s="8" t="n">
+      <c r="E189" s="6" t="n">
         <v>14601356012641.3</v>
       </c>
-      <c r="F189" s="8" t="n">
+      <c r="F189" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -9506,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9516,10 +9578,10 @@
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="B190" s="7" t="n">
+      <c r="B190" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C190" s="7" t="n">
+      <c r="C190" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -9527,10 +9589,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E190" s="8" t="n">
+      <c r="E190" s="6" t="n">
         <v>15490514782940.4</v>
       </c>
-      <c r="F190" s="8" t="n">
+      <c r="F190" s="6" t="n">
         <v>6.1</v>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -9555,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9565,10 +9627,10 @@
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="B191" s="7" t="n">
+      <c r="B191" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C191" s="7" t="n">
+      <c r="C191" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -9576,10 +9638,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E191" s="7" t="n">
+      <c r="E191" s="5" t="n">
         <v>16079339845626</v>
       </c>
-      <c r="F191" s="8" t="n">
+      <c r="F191" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -9604,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9614,10 +9676,10 @@
           <t>2023-05-01</t>
         </is>
       </c>
-      <c r="B192" s="7" t="n">
+      <c r="B192" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C192" s="7" t="n">
+      <c r="C192" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -9625,10 +9687,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E192" s="8" t="n">
+      <c r="E192" s="6" t="n">
         <v>16903293865395.6</v>
       </c>
-      <c r="F192" s="8" t="n">
+      <c r="F192" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -9653,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9663,10 +9725,10 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="B193" s="7" t="n">
+      <c r="B193" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C193" s="7" t="n">
+      <c r="C193" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -9674,10 +9736,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E193" s="8" t="n">
+      <c r="E193" s="6" t="n">
         <v>17944103145979.7</v>
       </c>
-      <c r="F193" s="8" t="n">
+      <c r="F193" s="6" t="n">
         <v>6.2</v>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -9702,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9712,10 +9774,10 @@
           <t>2023-07-01</t>
         </is>
       </c>
-      <c r="B194" s="7" t="n">
+      <c r="B194" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C194" s="7" t="n">
+      <c r="C194" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -9723,10 +9785,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E194" s="8" t="n">
+      <c r="E194" s="6" t="n">
         <v>19056534940064.7</v>
       </c>
-      <c r="F194" s="8" t="n">
+      <c r="F194" s="6" t="n">
         <v>6.2</v>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -9751,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9761,10 +9823,10 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="B195" s="7" t="n">
+      <c r="B195" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C195" s="7" t="n">
+      <c r="C195" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -9772,10 +9834,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E195" s="8" t="n">
+      <c r="E195" s="6" t="n">
         <v>20470345755220.7</v>
       </c>
-      <c r="F195" s="8" t="n">
+      <c r="F195" s="6" t="n">
         <v>7.4</v>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -9800,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9810,10 +9872,10 @@
           <t>2023-09-01</t>
         </is>
       </c>
-      <c r="B196" s="7" t="n">
+      <c r="B196" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C196" s="7" t="n">
+      <c r="C196" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -9821,10 +9883,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E196" s="8" t="n">
+      <c r="E196" s="6" t="n">
         <v>22244633245832.3</v>
       </c>
-      <c r="F196" s="8" t="n">
+      <c r="F196" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -9849,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9859,10 +9921,10 @@
           <t>2023-10-01</t>
         </is>
       </c>
-      <c r="B197" s="7" t="n">
+      <c r="B197" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C197" s="7" t="n">
+      <c r="C197" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -9870,10 +9932,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E197" s="8" t="n">
+      <c r="E197" s="6" t="n">
         <v>23547066398042.6</v>
       </c>
-      <c r="F197" s="8" t="n">
+      <c r="F197" s="6" t="n">
         <v>5.9</v>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -9898,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9908,10 +9970,10 @@
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="B198" s="7" t="n">
+      <c r="B198" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C198" s="7" t="n">
+      <c r="C198" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -9919,10 +9981,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E198" s="8" t="n">
+      <c r="E198" s="6" t="n">
         <v>24361617825691.9</v>
       </c>
-      <c r="F198" s="8" t="n">
+      <c r="F198" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -9947,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -9957,10 +10019,10 @@
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="B199" s="7" t="n">
+      <c r="B199" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C199" s="7" t="n">
+      <c r="C199" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -9968,10 +10030,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E199" s="8" t="n">
+      <c r="E199" s="6" t="n">
         <v>24952896762695.5</v>
       </c>
-      <c r="F199" s="8" t="n">
+      <c r="F199" s="6" t="n">
         <v>2.4</v>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -9996,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10006,10 +10068,10 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="B200" s="7" t="n">
+      <c r="B200" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C200" s="7" t="n">
+      <c r="C200" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -10017,10 +10079,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E200" s="8" t="n">
+      <c r="E200" s="6" t="n">
         <v>25379624724721.4</v>
       </c>
-      <c r="F200" s="8" t="n">
+      <c r="F200" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -10045,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10055,10 +10117,10 @@
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="B201" s="7" t="n">
+      <c r="B201" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C201" s="7" t="n">
+      <c r="C201" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -10066,10 +10128,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E201" s="8" t="n">
+      <c r="E201" s="6" t="n">
         <v>25684975429035.5</v>
       </c>
-      <c r="F201" s="8" t="n">
+      <c r="F201" s="6" t="n">
         <v>1.2</v>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -10094,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10104,10 +10166,10 @@
           <t>2024-03-01</t>
         </is>
       </c>
-      <c r="B202" s="7" t="n">
+      <c r="B202" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C202" s="7" t="n">
+      <c r="C202" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -10115,10 +10177,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E202" s="8" t="n">
+      <c r="E202" s="6" t="n">
         <v>25986417377849.1</v>
       </c>
-      <c r="F202" s="8" t="n">
+      <c r="F202" s="6" t="n">
         <v>1.2</v>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -10143,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10153,10 +10215,10 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="B203" s="7" t="n">
+      <c r="B203" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C203" s="7" t="n">
+      <c r="C203" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -10164,10 +10226,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E203" s="8" t="n">
+      <c r="E203" s="6" t="n">
         <v>26516834159241.7</v>
       </c>
-      <c r="F203" s="7" t="n">
+      <c r="F203" s="5" t="n">
         <v>2</v>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -10192,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10202,10 +10264,10 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="B204" s="7" t="n">
+      <c r="B204" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C204" s="7" t="n">
+      <c r="C204" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -10213,10 +10275,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E204" s="8" t="n">
+      <c r="E204" s="6" t="n">
         <v>26903972496868.1</v>
       </c>
-      <c r="F204" s="8" t="n">
+      <c r="F204" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -10241,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10251,10 +10313,10 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="B205" s="7" t="n">
+      <c r="B205" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C205" s="7" t="n">
+      <c r="C205" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -10262,10 +10324,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E205" s="8" t="n">
+      <c r="E205" s="6" t="n">
         <v>27162536873498.1</v>
       </c>
-      <c r="F205" s="7" t="n">
+      <c r="F205" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -10290,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10300,10 +10362,10 @@
           <t>2024-07-01</t>
         </is>
       </c>
-      <c r="B206" s="7" t="n">
+      <c r="B206" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C206" s="7" t="n">
+      <c r="C206" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -10311,10 +10373,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E206" s="8" t="n">
+      <c r="E206" s="6" t="n">
         <v>27366064708317.6</v>
       </c>
-      <c r="F206" s="8" t="n">
+      <c r="F206" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -10339,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10349,10 +10411,10 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="B207" s="7" t="n">
+      <c r="B207" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C207" s="7" t="n">
+      <c r="C207" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -10360,10 +10422,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E207" s="8" t="n">
+      <c r="E207" s="6" t="n">
         <v>27746667522384.2</v>
       </c>
-      <c r="F207" s="8" t="n">
+      <c r="F207" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -10388,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10398,10 +10460,10 @@
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B208" s="7" t="n">
+      <c r="B208" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C208" s="7" t="n">
+      <c r="C208" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -10409,10 +10471,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E208" s="8" t="n">
+      <c r="E208" s="6" t="n">
         <v>27972976631499.6</v>
       </c>
-      <c r="F208" s="8" t="n">
+      <c r="F208" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -10437,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10447,10 +10509,10 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="B209" s="7" t="n">
+      <c r="B209" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C209" s="7" t="n">
+      <c r="C209" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -10458,10 +10520,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E209" s="8" t="n">
+      <c r="E209" s="6" t="n">
         <v>29100339690082.1</v>
       </c>
-      <c r="F209" s="7" t="n">
+      <c r="F209" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -10486,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10496,10 +10558,10 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="B210" s="7" t="n">
+      <c r="B210" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C210" s="7" t="n">
+      <c r="C210" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -10507,10 +10569,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E210" s="8" t="n">
+      <c r="E210" s="6" t="n">
         <v>33516689669759.1</v>
       </c>
-      <c r="F210" s="8" t="n">
+      <c r="F210" s="6" t="n">
         <v>15.2</v>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -10535,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10545,10 +10607,10 @@
           <t>2024-12-01</t>
         </is>
       </c>
-      <c r="B211" s="7" t="n">
+      <c r="B211" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C211" s="7" t="n">
+      <c r="C211" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -10556,10 +10618,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E211" s="8" t="n">
+      <c r="E211" s="6" t="n">
         <v>36919909673224.9</v>
       </c>
-      <c r="F211" s="8" t="n">
+      <c r="F211" s="6" t="n">
         <v>10.2</v>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -10584,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10594,10 +10656,10 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="B212" s="7" t="n">
+      <c r="B212" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C212" s="7" t="n">
+      <c r="C212" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -10605,10 +10667,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E212" s="8" t="n">
+      <c r="E212" s="6" t="n">
         <v>40521840708458.3</v>
       </c>
-      <c r="F212" s="8" t="n">
+      <c r="F212" s="6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -10633,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10643,10 +10705,10 @@
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="B213" s="7" t="n">
+      <c r="B213" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C213" s="7" t="n">
+      <c r="C213" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -10654,10 +10716,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E213" s="8" t="n">
+      <c r="E213" s="6" t="n">
         <v>44948592993158.4</v>
       </c>
-      <c r="F213" s="8" t="n">
+      <c r="F213" s="6" t="n">
         <v>10.9</v>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -10682,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10692,10 +10754,10 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="B214" s="7" t="n">
+      <c r="B214" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C214" s="7" t="n">
+      <c r="C214" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -10703,10 +10765,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E214" s="8" t="n">
+      <c r="E214" s="6" t="n">
         <v>48695941027700.9</v>
       </c>
-      <c r="F214" s="8" t="n">
+      <c r="F214" s="6" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -10731,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10741,10 +10803,10 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="B215" s="7" t="n">
+      <c r="B215" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C215" s="7" t="n">
+      <c r="C215" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -10752,10 +10814,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E215" s="8" t="n">
+      <c r="E215" s="6" t="n">
         <v>56686369544411.3</v>
       </c>
-      <c r="F215" s="8" t="n">
+      <c r="F215" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -10780,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10790,10 +10852,10 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="B216" s="7" t="n">
+      <c r="B216" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C216" s="7" t="n">
+      <c r="C216" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -10801,10 +10863,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E216" s="8" t="n">
+      <c r="E216" s="6" t="n">
         <v>68691300824090.4</v>
       </c>
-      <c r="F216" s="8" t="n">
+      <c r="F216" s="6" t="n">
         <v>21.2</v>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -10829,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10839,10 +10901,10 @@
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="B217" s="7" t="n">
+      <c r="B217" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C217" s="7" t="n">
+      <c r="C217" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -10850,10 +10912,10 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="E217" s="8" t="n">
+      <c r="E217" s="6" t="n">
         <v>75780386243945.11</v>
       </c>
-      <c r="F217" s="8" t="n">
+      <c r="F217" s="6" t="n">
         <v>10.3</v>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -10878,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10888,10 +10950,10 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="B218" s="7" t="n">
+      <c r="B218" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C218" s="7" t="n">
+      <c r="C218" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -10899,10 +10961,10 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="E218" s="8" t="n">
+      <c r="E218" s="6" t="n">
         <v>86578516564082.41</v>
       </c>
-      <c r="F218" s="8" t="n">
+      <c r="F218" s="6" t="n">
         <v>14.2</v>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -10927,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10937,10 +10999,10 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="B219" s="7" t="n">
+      <c r="B219" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C219" s="7" t="n">
+      <c r="C219" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -10948,10 +11010,10 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="E219" s="7" t="n">
+      <c r="E219" s="6" t="n">
         <v>100503985890336</v>
       </c>
-      <c r="F219" s="8" t="n">
+      <c r="F219" s="6" t="n">
         <v>16.1</v>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -10976,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -10986,10 +11048,10 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="B220" s="7" t="n">
+      <c r="B220" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C220" s="7" t="n">
+      <c r="C220" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -10997,10 +11059,10 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="E220" s="7" t="n">
+      <c r="E220" s="6" t="n">
         <v>122169616603139</v>
       </c>
-      <c r="F220" s="8" t="n">
+      <c r="F220" s="6" t="n">
         <v>21.55698654224845</v>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -11025,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11035,10 +11097,10 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="B221" s="7" t="n">
+      <c r="B221" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C221" s="7" t="n">
+      <c r="C221" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -11046,10 +11108,10 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="E221" s="7" t="n">
+      <c r="E221" s="5" t="n">
         <v>153849788402697</v>
       </c>
-      <c r="F221" s="8" t="n">
+      <c r="F221" s="6" t="n">
         <v>25.93130164472011</v>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -11074,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11084,10 +11146,10 @@
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="B222" s="7" t="n">
+      <c r="B222" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C222" s="7" t="n">
+      <c r="C222" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -11095,10 +11157,10 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="E222" s="7" t="n">
+      <c r="E222" s="5" t="n">
         <v>187021825372618</v>
       </c>
-      <c r="F222" s="8" t="n">
+      <c r="F222" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -11123,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11133,10 +11195,10 @@
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="B223" s="7" t="n">
+      <c r="B223" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C223" s="7" t="n">
+      <c r="C223" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -11144,10 +11206,10 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="E223" s="7" t="n">
+      <c r="E223" s="6" t="n">
         <v>212393273459827</v>
       </c>
-      <c r="F223" s="8" t="n">
+      <c r="F223" s="6" t="n">
         <v>13.6</v>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -11172,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11182,10 +11244,10 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B224" s="7" t="n">
+      <c r="B224" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C224" s="7" t="n">
+      <c r="C224" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -11193,10 +11255,10 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="E224" s="7" t="n">
+      <c r="E224" s="5" t="n">
         <v>281565112063483</v>
       </c>
-      <c r="F224" s="8" t="n">
+      <c r="F224" s="6" t="n">
         <v>32.6</v>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -11221,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11231,10 +11293,10 @@
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B225" s="7" t="n">
+      <c r="B225" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C225" s="7" t="n">
+      <c r="C225" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -11242,10 +11304,10 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="E225" s="7" t="n">
+      <c r="E225" s="5" t="n">
         <v>322703709401564</v>
       </c>
-      <c r="F225" s="8" t="n">
+      <c r="F225" s="6" t="n">
         <v>14.6</v>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -11270,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11280,10 +11342,10 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="B226" s="7" t="n">
+      <c r="B226" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C226" s="7" t="n">
+      <c r="C226" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -11291,10 +11353,10 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="E226" s="7" t="n">
+      <c r="E226" s="5" t="n">
         <v>364960489482614</v>
       </c>
-      <c r="F226" s="8" t="n">
+      <c r="F226" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -11319,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11329,10 +11391,10 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="B227" s="7" t="n">
+      <c r="B227" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C227" s="7" t="n">
+      <c r="C227" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -11340,10 +11402,10 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="E227" s="7" t="n">
+      <c r="E227" s="5" t="n">
         <v>403528566746262</v>
       </c>
-      <c r="F227" s="8" t="n">
+      <c r="F227" s="6" t="n">
         <v>10.6</v>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -11368,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11378,10 +11440,10 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B228" s="7" t="n">
+      <c r="B228" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C228" s="7" t="n">
+      <c r="C228" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -11389,10 +11451,10 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="E228" s="8" t="n">
+      <c r="E228" s="6" t="n">
         <v>428967191622142.1</v>
       </c>
-      <c r="F228" s="8" t="n">
+      <c r="F228" s="6" t="n">
         <v>6.3</v>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -11417,7 +11479,56 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C229" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="n">
+        <v>488122054630450.1</v>
+      </c>
+      <c r="F229" s="6" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
@@ -11458,19 +11569,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>dataset_id</t>
         </is>
@@ -11482,7 +11593,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -11494,7 +11605,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -11506,7 +11617,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
@@ -11518,7 +11629,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -11530,7 +11641,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -11542,19 +11653,19 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>last_fetched_at</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T09:36:47Z</t>
+          <t>2026-07-17T14:53:24Z</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>first_date</t>
         </is>
@@ -11566,41 +11677,41 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>last_date</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>records</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>222</v>
+      <c r="B16" s="5" t="n">
+        <v>223</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-05-01", "year": 2026, "month": 5, "month_name": "Mayo", "index_value": 428967191622142.06, "monthly_variation_pct": 6.3, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-15T09:36:47Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-17T14:53:24Z"}</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17T14:53:24Z</t>
+          <t>2026-07-22T15:17:10Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-17T14:53:24Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-22T15:17:10Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:10Z</t>
+          <t>2026-07-22T21:35:44Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-22T15:17:10Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-22T21:35:44Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:44Z</t>
+          <t>2026-07-23T21:35:02Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-22T21:35:44Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-23T21:35:02Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:02Z</t>
+          <t>2026-07-24T21:36:07Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-23T21:35:02Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-24T21:36:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:07Z</t>
+          <t>2026-07-25T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-24T21:36:07Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-25T21:23:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:56Z</t>
+          <t>2026-07-26T21:25:45Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-25T21:23:56Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-26T21:25:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:45Z</t>
+          <t>2026-07-27T21:37:27Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-26T21:25:45Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-27T21:37:27Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:27Z</t>
+          <t>2026-07-28T21:37:46Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-27T21:37:27Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-28T21:37:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:46Z</t>
+          <t>2026-07-29T21:26:21Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-28T21:37:46Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-29T21:26:21Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:21Z</t>
+          <t>2026-07-30T21:40:54Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-29T21:26:21Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-30T21:40:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:54Z</t>
+          <t>2026-07-31T21:36:45Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-30T21:40:54Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-31T21:36:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:45Z</t>
+          <t>2026-08-01T21:23:56Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-07-31T21:36:45Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-01T21:23:56Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:56Z</t>
+          <t>2026-08-02T14:43:05Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-01T21:23:56Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-02T14:43:05Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:05Z</t>
+          <t>2026-08-02T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-02T14:43:05Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-02T21:23:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:57Z</t>
+          <t>2026-08-03T21:38:52Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-02T21:23:57Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-03T21:38:52Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03T21:38:52Z</t>
+          <t>2026-08-04T21:47:54Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-03T21:38:52Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-04T21:47:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:54Z</t>
+          <t>2026-08-05T21:44:20Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-04T21:47:54Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-05T21:44:20Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05T21:44:20Z</t>
+          <t>2026-08-07T00:56:55Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-05T21:44:20Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-07T00:56:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:55Z</t>
+          <t>2026-08-07T14:18:54Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-07T00:56:55Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-07T14:18:54Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T14:18:54Z</t>
+          <t>2026-08-07T21:09:09Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-07T14:18:54Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-07T21:09:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T21:09:09Z</t>
+          <t>2026-08-08T20:57:47Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-07T21:09:09Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-08T20:57:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:47Z</t>
+          <t>2026-08-09T21:02:01Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-08T20:57:47Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-09T21:02:01Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:02:01Z</t>
+          <t>2026-08-10T21:11:05Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-09T21:02:01Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-10T21:11:05Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10T21:11:05Z</t>
+          <t>2026-08-11T21:14:58Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-10T21:11:05Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-11T21:14:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11T21:14:58Z</t>
+          <t>2026-08-12T14:32:11Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-11T21:14:58Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-12T14:32:11Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T14:32:11Z</t>
+          <t>2026-08-12T21:12:47Z</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-12T14:32:11Z"}</t>
+          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-12T21:12:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K229"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,56 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="n">
+        <v>585239124308517.1</v>
+      </c>
+      <c r="F230" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>Índice base diciembre 2007=100 y variación mensual %</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls</t>
+        </is>
+      </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12T21:12:47Z</t>
+          <t>2026-08-13T21:12:32Z</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11733,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11744,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17">
@@ -11706,7 +11755,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-06-01", "year": 2026, "month": 6, "month_name": "Junio", "index_value": 488122054630450.06, "monthly_variation_pct": 13.8, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-12T21:12:47Z"}</t>
+          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-13T21:12:32Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13T21:12:32Z</t>
+          <t>2026-08-14T20:55:15Z</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-13T21:12:32Z"}</t>
+          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-14T20:55:15Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:55:15Z</t>
+          <t>2026-08-15T20:47:07Z</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-14T20:55:15Z"}</t>
+          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-15T20:47:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:47:07Z</t>
+          <t>2026-08-16T20:46:07Z</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-15T20:47:07Z"}</t>
+          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-16T20:46:07Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:46:07Z</t>
+          <t>2026-08-17T13:52:15Z</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-16T20:46:07Z"}</t>
+          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-17T13:52:15Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="K148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="K154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="K158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="K160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="K198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="K200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="K202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="K208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="K220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="K222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="K224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="K226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="K228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:52:15Z</t>
+          <t>2026-08-17T20:52:46Z</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-17T13:52:15Z"}</t>
+          <t>{"date": "2026-07-01", "year": 2026, "month": 7, "month_name": "Julio", "index_value": 585239124308517.1, "monthly_variation_pct": 19.9, "unit": "Índice base diciembre 2007=100 y variación mensual %", "frequency": "monthly", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/precios_consumidor/4_5_7_2.xls", "fetched_at": "2026-08-17T20:52:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_inpc_nacional_mensual.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17T20:52:46Z</t>
+          <t>2026-08-21T16:34:23Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="K138" s="4" t="inlineStr">
      